--- a/events/Ivrea_2017_WC/Ivrea_2017_WC_start.xlsx
+++ b/events/Ivrea_2017_WC/Ivrea_2017_WC_start.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W572"/>
+  <dimension ref="A1:AC572"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,17 +519,47 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Name4</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Name5</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Name6</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
           <t>ICF_ID1</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>ICF_ID2</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>ICF_ID3</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>ICF_ID4</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>ICF_ID5</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>ICF_ID6</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1067,12 @@
           <t>QUERCI Alberto</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>39904</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>39906</t>
         </is>
@@ -1105,12 +1135,12 @@
           <t>HEGER Tomas</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>68872</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>42007</t>
         </is>
@@ -1173,12 +1203,12 @@
           <t>GEWISSLER Matus</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>39248</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>39249</t>
         </is>
@@ -1241,12 +1271,12 @@
           <t>HOCHSCHORNER Peter</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>35356</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>35357</t>
         </is>
@@ -1309,12 +1339,12 @@
           <t>FERRARI Niccolo</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>35497</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>35498</t>
         </is>
@@ -1377,12 +1407,12 @@
           <t>VRZAN Jakub</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>35042</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>35043</t>
         </is>
@@ -1445,12 +1475,12 @@
           <t>WERRO Simon</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>35424</t>
         </is>
@@ -1513,12 +1543,12 @@
           <t>BATIK Jan</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>35368</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>35367</t>
         </is>
@@ -1581,12 +1611,12 @@
           <t>TILLARD Pierre-Antoine</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>35379</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>35413</t>
         </is>
@@ -1649,12 +1679,12 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>35145</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -1717,12 +1747,12 @@
           <t>BISO Hugo</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>35403</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>35229</t>
         </is>
@@ -1785,12 +1815,12 @@
           <t>CAILHOL Hugo</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>35476</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>35491</t>
         </is>
@@ -1853,12 +1883,12 @@
           <t>BECKER Thomas</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>35139</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>35143</t>
         </is>
@@ -1921,12 +1951,12 @@
           <t>PECHE Matthieu</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>35350</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>35400</t>
         </is>
@@ -1989,12 +2019,12 @@
           <t>SINDLER Marek</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>35062</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>35063</t>
         </is>
@@ -2057,12 +2087,12 @@
           <t>SKANTAR Peter</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>35360</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>35361</t>
         </is>
@@ -2120,7 +2150,7 @@
           <t>HAVLICKOVA Katerina</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>35048</t>
         </is>
@@ -2178,7 +2208,7 @@
           <t>BERTONCELLI Marta</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>71982</t>
         </is>
@@ -2236,7 +2266,7 @@
           <t>BORGHI Elena</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>75493</t>
         </is>
@@ -2294,7 +2324,7 @@
           <t>FORROW Bethan</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>69065</t>
         </is>
@@ -2352,7 +2382,7 @@
           <t>SPICER Phoebe</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>75827</t>
         </is>
@@ -2410,7 +2440,7 @@
           <t>DIESKOVA Eva</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>71639</t>
         </is>
@@ -2521,7 +2551,7 @@
           <t>BAYLACQ Oceane</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>69444</t>
         </is>
@@ -2632,7 +2662,7 @@
           <t>SATO Ayano</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>60374</t>
         </is>
@@ -2690,7 +2720,7 @@
           <t>DONNELLY Sage</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>60119</t>
         </is>
@@ -2748,7 +2778,7 @@
           <t>YAGI Airi</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>37756</t>
         </is>
@@ -2859,7 +2889,7 @@
           <t>PELLICER CHICA Laura</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>43129</t>
         </is>
@@ -2917,7 +2947,7 @@
           <t>DANIELS Haley</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>36260</t>
         </is>
@@ -2975,7 +3005,7 @@
           <t>KOZOROG Alja</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>39986</t>
         </is>
@@ -3033,7 +3063,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -3091,7 +3121,7 @@
           <t>BIZJAK Nina</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>39984</t>
         </is>
@@ -3202,7 +3232,7 @@
           <t>OHMAYER Birgit</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>39157</t>
         </is>
@@ -3260,7 +3290,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -3318,7 +3348,7 @@
           <t>STANOVSKA Sona</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>51647</t>
         </is>
@@ -3376,7 +3406,7 @@
           <t>HERZOG Andrea</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>55099</t>
         </is>
@@ -3434,7 +3464,7 @@
           <t>MACEKOVA Simona</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>45153</t>
         </is>
@@ -3492,7 +3522,7 @@
           <t>OLAZABAL Klara</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>43985</t>
         </is>
@@ -3550,7 +3580,7 @@
           <t>TIXIER Cecile</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>35687</t>
         </is>
@@ -3608,7 +3638,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -3666,7 +3696,7 @@
           <t>JANCOVA Monika</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>36015</t>
         </is>
@@ -3724,7 +3754,7 @@
           <t>STOECKLIN Lena</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>35822</t>
         </is>
@@ -3782,7 +3812,7 @@
           <t>PRIOUX Lucie</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>42984</t>
         </is>
@@ -3840,7 +3870,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -3951,7 +3981,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -4009,7 +4039,7 @@
           <t>WERATSCHNIG Nadine</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>41613</t>
         </is>
@@ -4067,7 +4097,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -4178,7 +4208,7 @@
           <t>JACQUET Claire</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>35684</t>
         </is>
@@ -4236,7 +4266,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U64" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -4294,7 +4324,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr">
+      <c r="X65" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -4405,7 +4435,7 @@
           <t>OLIVEIRA Anderson</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr">
+      <c r="X67" t="inlineStr">
         <is>
           <t>38020</t>
         </is>
@@ -4463,7 +4493,7 @@
           <t>O'FERRALL Tadhg</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr">
+      <c r="X68" t="inlineStr">
         <is>
           <t>51944</t>
         </is>
@@ -4521,7 +4551,7 @@
           <t>LAUMONDAIS Louison</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr">
+      <c r="X69" t="inlineStr">
         <is>
           <t>77268</t>
         </is>
@@ -4579,7 +4609,7 @@
           <t>ATKINS Austin</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr">
+      <c r="X70" t="inlineStr">
         <is>
           <t>80421</t>
         </is>
@@ -4637,7 +4667,7 @@
           <t>PITTMAN Taylor</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr">
+      <c r="X71" t="inlineStr">
         <is>
           <t>69137</t>
         </is>
@@ -4695,7 +4725,7 @@
           <t>MUTO Yusuke</t>
         </is>
       </c>
-      <c r="U72" t="inlineStr">
+      <c r="X72" t="inlineStr">
         <is>
           <t>71820</t>
         </is>
@@ -4753,7 +4783,7 @@
           <t>JOSEPH Joshua</t>
         </is>
       </c>
-      <c r="U73" t="inlineStr">
+      <c r="X73" t="inlineStr">
         <is>
           <t>69141</t>
         </is>
@@ -4811,7 +4841,7 @@
           <t>MATEJKA Michael</t>
         </is>
       </c>
-      <c r="U74" t="inlineStr">
+      <c r="X74" t="inlineStr">
         <is>
           <t>36118</t>
         </is>
@@ -4869,7 +4899,7 @@
           <t>McCREERY Alistair</t>
         </is>
       </c>
-      <c r="U75" t="inlineStr">
+      <c r="X75" t="inlineStr">
         <is>
           <t>60125</t>
         </is>
@@ -4927,7 +4957,7 @@
           <t>ALVARENGA Frederico</t>
         </is>
       </c>
-      <c r="U76" t="inlineStr">
+      <c r="X76" t="inlineStr">
         <is>
           <t>71976</t>
         </is>
@@ -4985,7 +5015,7 @@
           <t>VIANELLO Marco</t>
         </is>
       </c>
-      <c r="U77" t="inlineStr">
+      <c r="X77" t="inlineStr">
         <is>
           <t>54910</t>
         </is>
@@ -5043,7 +5073,7 @@
           <t>MADORE Mathurin</t>
         </is>
       </c>
-      <c r="U78" t="inlineStr">
+      <c r="X78" t="inlineStr">
         <is>
           <t>51994</t>
         </is>
@@ -5101,7 +5131,7 @@
           <t>MARX Dimitri</t>
         </is>
       </c>
-      <c r="U79" t="inlineStr">
+      <c r="X79" t="inlineStr">
         <is>
           <t>60326</t>
         </is>
@@ -5159,7 +5189,7 @@
           <t>KUDER MARUSIC Vid</t>
         </is>
       </c>
-      <c r="U80" t="inlineStr">
+      <c r="X80" t="inlineStr">
         <is>
           <t>44342</t>
         </is>
@@ -5270,7 +5300,7 @@
           <t>ECHEVERRIA OLGUIN Andraz</t>
         </is>
       </c>
-      <c r="U82" t="inlineStr">
+      <c r="X82" t="inlineStr">
         <is>
           <t>41646</t>
         </is>
@@ -5328,7 +5358,7 @@
           <t>TEAGUE Eoin</t>
         </is>
       </c>
-      <c r="U83" t="inlineStr">
+      <c r="X83" t="inlineStr">
         <is>
           <t>37913</t>
         </is>
@@ -5386,7 +5416,7 @@
           <t>SLEEBUS Axel</t>
         </is>
       </c>
-      <c r="U84" t="inlineStr">
+      <c r="X84" t="inlineStr">
         <is>
           <t>42892</t>
         </is>
@@ -5444,7 +5474,7 @@
           <t>KARLSSON Max</t>
         </is>
       </c>
-      <c r="U85" t="inlineStr">
+      <c r="X85" t="inlineStr">
         <is>
           <t>35111</t>
         </is>
@@ -5502,7 +5532,7 @@
           <t>ZIMA Tomas</t>
         </is>
       </c>
-      <c r="U86" t="inlineStr">
+      <c r="X86" t="inlineStr">
         <is>
           <t>60019</t>
         </is>
@@ -5560,7 +5590,7 @@
           <t>MIKO Radoslav</t>
         </is>
       </c>
-      <c r="U87" t="inlineStr">
+      <c r="X87" t="inlineStr">
         <is>
           <t>71930</t>
         </is>
@@ -5618,7 +5648,7 @@
           <t>LEE EDWARDS Ciaran</t>
         </is>
       </c>
-      <c r="U88" t="inlineStr">
+      <c r="X88" t="inlineStr">
         <is>
           <t>35614</t>
         </is>
@@ -5676,7 +5706,7 @@
           <t>OLAZABAL Telmo</t>
         </is>
       </c>
-      <c r="U89" t="inlineStr">
+      <c r="X89" t="inlineStr">
         <is>
           <t>38782</t>
         </is>
@@ -5734,7 +5764,7 @@
           <t>MAPELLI Guilherme Marcello</t>
         </is>
       </c>
-      <c r="U90" t="inlineStr">
+      <c r="X90" t="inlineStr">
         <is>
           <t>38015</t>
         </is>
@@ -5792,7 +5822,7 @@
           <t>FORD David</t>
         </is>
       </c>
-      <c r="U91" t="inlineStr">
+      <c r="X91" t="inlineStr">
         <is>
           <t>35532</t>
         </is>
@@ -5850,7 +5880,7 @@
           <t>WAHLEN Fredrik</t>
         </is>
       </c>
-      <c r="U92" t="inlineStr">
+      <c r="X92" t="inlineStr">
         <is>
           <t>35102</t>
         </is>
@@ -5908,7 +5938,7 @@
           <t>TAYLER Michael</t>
         </is>
       </c>
-      <c r="U93" t="inlineStr">
+      <c r="X93" t="inlineStr">
         <is>
           <t>36262</t>
         </is>
@@ -5966,7 +5996,7 @@
           <t>BURGI Quentin</t>
         </is>
       </c>
-      <c r="U94" t="inlineStr">
+      <c r="X94" t="inlineStr">
         <is>
           <t>41590</t>
         </is>
@@ -6024,7 +6054,7 @@
           <t>MACUS Richard</t>
         </is>
       </c>
-      <c r="U95" t="inlineStr">
+      <c r="X95" t="inlineStr">
         <is>
           <t>42855</t>
         </is>
@@ -6082,7 +6112,7 @@
           <t>SILVA Ivan</t>
         </is>
       </c>
-      <c r="U96" t="inlineStr">
+      <c r="X96" t="inlineStr">
         <is>
           <t>35482</t>
         </is>
@@ -6140,7 +6170,7 @@
           <t>WERRO Lukas</t>
         </is>
       </c>
-      <c r="U97" t="inlineStr">
+      <c r="X97" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
@@ -6198,7 +6228,7 @@
           <t>SWETNAM Huw</t>
         </is>
       </c>
-      <c r="U98" t="inlineStr">
+      <c r="X98" t="inlineStr">
         <is>
           <t>35652</t>
         </is>
@@ -6256,7 +6286,7 @@
           <t>JAKSE Zan</t>
         </is>
       </c>
-      <c r="U99" t="inlineStr">
+      <c r="X99" t="inlineStr">
         <is>
           <t>44340</t>
         </is>
@@ -6314,7 +6344,7 @@
           <t>DRAPER Warwick</t>
         </is>
       </c>
-      <c r="U100" t="inlineStr">
+      <c r="X100" t="inlineStr">
         <is>
           <t>36536</t>
         </is>
@@ -6372,7 +6402,7 @@
           <t>YAZAWA Kazuki</t>
         </is>
       </c>
-      <c r="U101" t="inlineStr">
+      <c r="X101" t="inlineStr">
         <is>
           <t>36482</t>
         </is>
@@ -6430,7 +6460,7 @@
           <t>WEGER Jakob</t>
         </is>
       </c>
-      <c r="U102" t="inlineStr">
+      <c r="X102" t="inlineStr">
         <is>
           <t>54909</t>
         </is>
@@ -6488,7 +6518,7 @@
           <t>PASIUT Michal</t>
         </is>
       </c>
-      <c r="U103" t="inlineStr">
+      <c r="X103" t="inlineStr">
         <is>
           <t>35095</t>
         </is>
@@ -6546,7 +6576,7 @@
           <t>WEGER Matthias</t>
         </is>
       </c>
-      <c r="U104" t="inlineStr">
+      <c r="X104" t="inlineStr">
         <is>
           <t>68837</t>
         </is>
@@ -6604,7 +6634,7 @@
           <t>TSVIET Igor</t>
         </is>
       </c>
-      <c r="U105" t="inlineStr">
+      <c r="X105" t="inlineStr">
         <is>
           <t>35527</t>
         </is>
@@ -6715,7 +6745,7 @@
           <t>HOLMER Erik</t>
         </is>
       </c>
-      <c r="U107" t="inlineStr">
+      <c r="X107" t="inlineStr">
         <is>
           <t>35104</t>
         </is>
@@ -6773,7 +6803,7 @@
           <t>BUTCHER Finn</t>
         </is>
       </c>
-      <c r="U108" t="inlineStr">
+      <c r="X108" t="inlineStr">
         <is>
           <t>36663</t>
         </is>
@@ -6831,7 +6861,7 @@
           <t>CADENA Jordi</t>
         </is>
       </c>
-      <c r="U109" t="inlineStr">
+      <c r="X109" t="inlineStr">
         <is>
           <t>41644</t>
         </is>
@@ -6889,7 +6919,7 @@
           <t>POTOCNY Marcel</t>
         </is>
       </c>
-      <c r="U110" t="inlineStr">
+      <c r="X110" t="inlineStr">
         <is>
           <t>35235</t>
         </is>
@@ -6947,7 +6977,7 @@
           <t>GILBERT Callum</t>
         </is>
       </c>
-      <c r="U111" t="inlineStr">
+      <c r="X111" t="inlineStr">
         <is>
           <t>42090</t>
         </is>
@@ -7058,7 +7088,7 @@
           <t>LEITNER Mario</t>
         </is>
       </c>
-      <c r="U113" t="inlineStr">
+      <c r="X113" t="inlineStr">
         <is>
           <t>35546</t>
         </is>
@@ -7116,7 +7146,7 @@
           <t>DOUGOUD Martin</t>
         </is>
       </c>
-      <c r="U114" t="inlineStr">
+      <c r="X114" t="inlineStr">
         <is>
           <t>35426</t>
         </is>
@@ -7174,7 +7204,7 @@
           <t>SRABOTNIK Martin</t>
         </is>
       </c>
-      <c r="U115" t="inlineStr">
+      <c r="X115" t="inlineStr">
         <is>
           <t>39080</t>
         </is>
@@ -7232,7 +7262,7 @@
           <t>OKREGLAK Maciej</t>
         </is>
       </c>
-      <c r="U116" t="inlineStr">
+      <c r="X116" t="inlineStr">
         <is>
           <t>35088</t>
         </is>
@@ -7290,7 +7320,7 @@
           <t>DAWSON Mike</t>
         </is>
       </c>
-      <c r="U117" t="inlineStr">
+      <c r="X117" t="inlineStr">
         <is>
           <t>36656</t>
         </is>
@@ -7401,7 +7431,7 @@
           <t>ADACHI Kazuya</t>
         </is>
       </c>
-      <c r="U119" t="inlineStr">
+      <c r="X119" t="inlineStr">
         <is>
           <t>36646</t>
         </is>
@@ -7459,7 +7489,7 @@
           <t>IVALDI Zeno</t>
         </is>
       </c>
-      <c r="U120" t="inlineStr">
+      <c r="X120" t="inlineStr">
         <is>
           <t>35480</t>
         </is>
@@ -7517,7 +7547,7 @@
           <t>CRESPO Joan</t>
         </is>
       </c>
-      <c r="U121" t="inlineStr">
+      <c r="X121" t="inlineStr">
         <is>
           <t>35749</t>
         </is>
@@ -7575,7 +7605,7 @@
           <t>DOBY Mathieu</t>
         </is>
       </c>
-      <c r="U122" t="inlineStr">
+      <c r="X122" t="inlineStr">
         <is>
           <t>35292</t>
         </is>
@@ -7633,7 +7663,7 @@
           <t>SCHWEIKERT Fabian</t>
         </is>
       </c>
-      <c r="U123" t="inlineStr">
+      <c r="X123" t="inlineStr">
         <is>
           <t>38412</t>
         </is>
@@ -7691,7 +7721,7 @@
           <t>HRADILEK Vavrinec</t>
         </is>
       </c>
-      <c r="U124" t="inlineStr">
+      <c r="X124" t="inlineStr">
         <is>
           <t>35031</t>
         </is>
@@ -7749,7 +7779,7 @@
           <t>POPIELA Dariusz</t>
         </is>
       </c>
-      <c r="U125" t="inlineStr">
+      <c r="X125" t="inlineStr">
         <is>
           <t>35096</t>
         </is>
@@ -7807,7 +7837,7 @@
           <t>SMOLEN Michal</t>
         </is>
       </c>
-      <c r="U126" t="inlineStr">
+      <c r="X126" t="inlineStr">
         <is>
           <t>36397</t>
         </is>
@@ -7865,7 +7895,7 @@
           <t>GRIMM Alexander</t>
         </is>
       </c>
-      <c r="U127" t="inlineStr">
+      <c r="X127" t="inlineStr">
         <is>
           <t>35112</t>
         </is>
@@ -7923,7 +7953,7 @@
           <t>BIAZIZZO Mathieu</t>
         </is>
       </c>
-      <c r="U128" t="inlineStr">
+      <c r="X128" t="inlineStr">
         <is>
           <t>35484</t>
         </is>
@@ -7981,7 +8011,7 @@
           <t>DELFOUR Lucien</t>
         </is>
       </c>
-      <c r="U129" t="inlineStr">
+      <c r="X129" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
@@ -8039,7 +8069,7 @@
           <t>BERSINGER Thomas</t>
         </is>
       </c>
-      <c r="U130" t="inlineStr">
+      <c r="X130" t="inlineStr">
         <is>
           <t>35228</t>
         </is>
@@ -8097,7 +8127,7 @@
           <t>DE GENNARO Giovanni</t>
         </is>
       </c>
-      <c r="U131" t="inlineStr">
+      <c r="X131" t="inlineStr">
         <is>
           <t>35244</t>
         </is>
@@ -8155,7 +8185,7 @@
           <t>SCHUBERT Sebastian</t>
         </is>
       </c>
-      <c r="U132" t="inlineStr">
+      <c r="X132" t="inlineStr">
         <is>
           <t>35114</t>
         </is>
@@ -8213,7 +8243,7 @@
           <t>GRIGAR Jakub</t>
         </is>
       </c>
-      <c r="U133" t="inlineStr">
+      <c r="X133" t="inlineStr">
         <is>
           <t>37284</t>
         </is>
@@ -8271,7 +8301,7 @@
           <t>AIGNER Hannes</t>
         </is>
       </c>
-      <c r="U134" t="inlineStr">
+      <c r="X134" t="inlineStr">
         <is>
           <t>35115</t>
         </is>
@@ -8329,7 +8359,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U135" t="inlineStr">
+      <c r="X135" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -8387,7 +8417,7 @@
           <t>PRINDIS Vit</t>
         </is>
       </c>
-      <c r="U136" t="inlineStr">
+      <c r="X136" t="inlineStr">
         <is>
           <t>35065</t>
         </is>
@@ -8450,12 +8480,12 @@
           <t>BECKER Thomas</t>
         </is>
       </c>
-      <c r="U137" t="inlineStr">
+      <c r="X137" t="inlineStr">
         <is>
           <t>35139</t>
         </is>
       </c>
-      <c r="V137" t="inlineStr">
+      <c r="Y137" t="inlineStr">
         <is>
           <t>35143</t>
         </is>
@@ -8513,7 +8543,7 @@
           <t>BERTONCELLI Marta</t>
         </is>
       </c>
-      <c r="U138" t="inlineStr">
+      <c r="X138" t="inlineStr">
         <is>
           <t>71982</t>
         </is>
@@ -8571,7 +8601,7 @@
           <t>FORROW Bethan</t>
         </is>
       </c>
-      <c r="U139" t="inlineStr">
+      <c r="X139" t="inlineStr">
         <is>
           <t>69065</t>
         </is>
@@ -8629,7 +8659,7 @@
           <t>DIESKOVA Eva</t>
         </is>
       </c>
-      <c r="U140" t="inlineStr">
+      <c r="X140" t="inlineStr">
         <is>
           <t>71639</t>
         </is>
@@ -8740,7 +8770,7 @@
           <t>BAYLACQ Oceane</t>
         </is>
       </c>
-      <c r="U142" t="inlineStr">
+      <c r="X142" t="inlineStr">
         <is>
           <t>69444</t>
         </is>
@@ -8851,7 +8881,7 @@
           <t>SATO Ayano</t>
         </is>
       </c>
-      <c r="U144" t="inlineStr">
+      <c r="X144" t="inlineStr">
         <is>
           <t>60374</t>
         </is>
@@ -8909,7 +8939,7 @@
           <t>YAGI Airi</t>
         </is>
       </c>
-      <c r="U145" t="inlineStr">
+      <c r="X145" t="inlineStr">
         <is>
           <t>37756</t>
         </is>
@@ -9020,7 +9050,7 @@
           <t>PELLICER CHICA Laura</t>
         </is>
       </c>
-      <c r="U147" t="inlineStr">
+      <c r="X147" t="inlineStr">
         <is>
           <t>43129</t>
         </is>
@@ -9078,7 +9108,7 @@
           <t>DANIELS Haley</t>
         </is>
       </c>
-      <c r="U148" t="inlineStr">
+      <c r="X148" t="inlineStr">
         <is>
           <t>36260</t>
         </is>
@@ -9136,7 +9166,7 @@
           <t>KOZOROG Alja</t>
         </is>
       </c>
-      <c r="U149" t="inlineStr">
+      <c r="X149" t="inlineStr">
         <is>
           <t>39986</t>
         </is>
@@ -9194,7 +9224,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U150" t="inlineStr">
+      <c r="X150" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -9252,7 +9282,7 @@
           <t>BIZJAK Nina</t>
         </is>
       </c>
-      <c r="U151" t="inlineStr">
+      <c r="X151" t="inlineStr">
         <is>
           <t>39984</t>
         </is>
@@ -9363,7 +9393,7 @@
           <t>OHMAYER Birgit</t>
         </is>
       </c>
-      <c r="U153" t="inlineStr">
+      <c r="X153" t="inlineStr">
         <is>
           <t>39157</t>
         </is>
@@ -9421,7 +9451,7 @@
           <t>HERZOG Andrea</t>
         </is>
       </c>
-      <c r="U154" t="inlineStr">
+      <c r="X154" t="inlineStr">
         <is>
           <t>55099</t>
         </is>
@@ -9479,7 +9509,7 @@
           <t>OLAZABAL Klara</t>
         </is>
       </c>
-      <c r="U155" t="inlineStr">
+      <c r="X155" t="inlineStr">
         <is>
           <t>43985</t>
         </is>
@@ -9537,7 +9567,7 @@
           <t>STOECKLIN Lena</t>
         </is>
       </c>
-      <c r="U156" t="inlineStr">
+      <c r="X156" t="inlineStr">
         <is>
           <t>35822</t>
         </is>
@@ -9648,7 +9678,7 @@
           <t>OLIVEIRA Anderson</t>
         </is>
       </c>
-      <c r="U158" t="inlineStr">
+      <c r="X158" t="inlineStr">
         <is>
           <t>38020</t>
         </is>
@@ -9706,7 +9736,7 @@
           <t>O'FERRALL Tadhg</t>
         </is>
       </c>
-      <c r="U159" t="inlineStr">
+      <c r="X159" t="inlineStr">
         <is>
           <t>51944</t>
         </is>
@@ -9764,7 +9794,7 @@
           <t>LAUMONDAIS Louison</t>
         </is>
       </c>
-      <c r="U160" t="inlineStr">
+      <c r="X160" t="inlineStr">
         <is>
           <t>77268</t>
         </is>
@@ -9822,7 +9852,7 @@
           <t>ATKINS Austin</t>
         </is>
       </c>
-      <c r="U161" t="inlineStr">
+      <c r="X161" t="inlineStr">
         <is>
           <t>80421</t>
         </is>
@@ -9880,7 +9910,7 @@
           <t>PITTMAN Taylor</t>
         </is>
       </c>
-      <c r="U162" t="inlineStr">
+      <c r="X162" t="inlineStr">
         <is>
           <t>69137</t>
         </is>
@@ -9938,7 +9968,7 @@
           <t>MUTO Yusuke</t>
         </is>
       </c>
-      <c r="U163" t="inlineStr">
+      <c r="X163" t="inlineStr">
         <is>
           <t>71820</t>
         </is>
@@ -9996,7 +10026,7 @@
           <t>JOSEPH Joshua</t>
         </is>
       </c>
-      <c r="U164" t="inlineStr">
+      <c r="X164" t="inlineStr">
         <is>
           <t>69141</t>
         </is>
@@ -10054,7 +10084,7 @@
           <t>MATEJKA Michael</t>
         </is>
       </c>
-      <c r="U165" t="inlineStr">
+      <c r="X165" t="inlineStr">
         <is>
           <t>36118</t>
         </is>
@@ -10112,7 +10142,7 @@
           <t>McCREERY Alistair</t>
         </is>
       </c>
-      <c r="U166" t="inlineStr">
+      <c r="X166" t="inlineStr">
         <is>
           <t>60125</t>
         </is>
@@ -10170,7 +10200,7 @@
           <t>ALVARENGA Frederico</t>
         </is>
       </c>
-      <c r="U167" t="inlineStr">
+      <c r="X167" t="inlineStr">
         <is>
           <t>71976</t>
         </is>
@@ -10228,7 +10258,7 @@
           <t>VIANELLO Marco</t>
         </is>
       </c>
-      <c r="U168" t="inlineStr">
+      <c r="X168" t="inlineStr">
         <is>
           <t>54910</t>
         </is>
@@ -10286,7 +10316,7 @@
           <t>MADORE Mathurin</t>
         </is>
       </c>
-      <c r="U169" t="inlineStr">
+      <c r="X169" t="inlineStr">
         <is>
           <t>51994</t>
         </is>
@@ -10344,7 +10374,7 @@
           <t>MARX Dimitri</t>
         </is>
       </c>
-      <c r="U170" t="inlineStr">
+      <c r="X170" t="inlineStr">
         <is>
           <t>60326</t>
         </is>
@@ -10402,7 +10432,7 @@
           <t>KUDER MARUSIC Vid</t>
         </is>
       </c>
-      <c r="U171" t="inlineStr">
+      <c r="X171" t="inlineStr">
         <is>
           <t>44342</t>
         </is>
@@ -10460,7 +10490,7 @@
           <t>ECHEVERRIA OLGUIN Andraz</t>
         </is>
       </c>
-      <c r="U172" t="inlineStr">
+      <c r="X172" t="inlineStr">
         <is>
           <t>41646</t>
         </is>
@@ -10518,7 +10548,7 @@
           <t>TEAGUE Eoin</t>
         </is>
       </c>
-      <c r="U173" t="inlineStr">
+      <c r="X173" t="inlineStr">
         <is>
           <t>37913</t>
         </is>
@@ -10576,7 +10606,7 @@
           <t>SLEEBUS Axel</t>
         </is>
       </c>
-      <c r="U174" t="inlineStr">
+      <c r="X174" t="inlineStr">
         <is>
           <t>42892</t>
         </is>
@@ -10634,7 +10664,7 @@
           <t>KARLSSON Max</t>
         </is>
       </c>
-      <c r="U175" t="inlineStr">
+      <c r="X175" t="inlineStr">
         <is>
           <t>35111</t>
         </is>
@@ -10692,7 +10722,7 @@
           <t>MIKO Radoslav</t>
         </is>
       </c>
-      <c r="U176" t="inlineStr">
+      <c r="X176" t="inlineStr">
         <is>
           <t>71930</t>
         </is>
@@ -10750,7 +10780,7 @@
           <t>LEE EDWARDS Ciaran</t>
         </is>
       </c>
-      <c r="U177" t="inlineStr">
+      <c r="X177" t="inlineStr">
         <is>
           <t>35614</t>
         </is>
@@ -10808,7 +10838,7 @@
           <t>OLAZABAL Telmo</t>
         </is>
       </c>
-      <c r="U178" t="inlineStr">
+      <c r="X178" t="inlineStr">
         <is>
           <t>38782</t>
         </is>
@@ -10866,7 +10896,7 @@
           <t>MAPELLI Guilherme Marcello</t>
         </is>
       </c>
-      <c r="U179" t="inlineStr">
+      <c r="X179" t="inlineStr">
         <is>
           <t>38015</t>
         </is>
@@ -10924,7 +10954,7 @@
           <t>FORD David</t>
         </is>
       </c>
-      <c r="U180" t="inlineStr">
+      <c r="X180" t="inlineStr">
         <is>
           <t>35532</t>
         </is>
@@ -10982,7 +11012,7 @@
           <t>WAHLEN Fredrik</t>
         </is>
       </c>
-      <c r="U181" t="inlineStr">
+      <c r="X181" t="inlineStr">
         <is>
           <t>35102</t>
         </is>
@@ -11040,7 +11070,7 @@
           <t>TAYLER Michael</t>
         </is>
       </c>
-      <c r="U182" t="inlineStr">
+      <c r="X182" t="inlineStr">
         <is>
           <t>36262</t>
         </is>
@@ -11098,7 +11128,7 @@
           <t>MACUS Richard</t>
         </is>
       </c>
-      <c r="U183" t="inlineStr">
+      <c r="X183" t="inlineStr">
         <is>
           <t>42855</t>
         </is>
@@ -11156,7 +11186,7 @@
           <t>SILVA Ivan</t>
         </is>
       </c>
-      <c r="U184" t="inlineStr">
+      <c r="X184" t="inlineStr">
         <is>
           <t>35482</t>
         </is>
@@ -11214,7 +11244,7 @@
           <t>SWETNAM Huw</t>
         </is>
       </c>
-      <c r="U185" t="inlineStr">
+      <c r="X185" t="inlineStr">
         <is>
           <t>35652</t>
         </is>
@@ -11272,7 +11302,7 @@
           <t>DRAPER Warwick</t>
         </is>
       </c>
-      <c r="U186" t="inlineStr">
+      <c r="X186" t="inlineStr">
         <is>
           <t>36536</t>
         </is>
@@ -11330,7 +11360,7 @@
           <t>WEGER Matthias</t>
         </is>
       </c>
-      <c r="U187" t="inlineStr">
+      <c r="X187" t="inlineStr">
         <is>
           <t>68837</t>
         </is>
@@ -11388,7 +11418,7 @@
           <t>TSVIET Igor</t>
         </is>
       </c>
-      <c r="U188" t="inlineStr">
+      <c r="X188" t="inlineStr">
         <is>
           <t>35527</t>
         </is>
@@ -11499,7 +11529,7 @@
           <t>BUTCHER Finn</t>
         </is>
       </c>
-      <c r="U190" t="inlineStr">
+      <c r="X190" t="inlineStr">
         <is>
           <t>36663</t>
         </is>
@@ -11557,7 +11587,7 @@
           <t>POTOCNY Marcel</t>
         </is>
       </c>
-      <c r="U191" t="inlineStr">
+      <c r="X191" t="inlineStr">
         <is>
           <t>35235</t>
         </is>
@@ -11615,7 +11645,7 @@
           <t>GILBERT Callum</t>
         </is>
       </c>
-      <c r="U192" t="inlineStr">
+      <c r="X192" t="inlineStr">
         <is>
           <t>42090</t>
         </is>
@@ -11726,7 +11756,7 @@
           <t>DAWSON Mike</t>
         </is>
       </c>
-      <c r="U194" t="inlineStr">
+      <c r="X194" t="inlineStr">
         <is>
           <t>36656</t>
         </is>
@@ -11784,7 +11814,7 @@
           <t>DOBY Mathieu</t>
         </is>
       </c>
-      <c r="U195" t="inlineStr">
+      <c r="X195" t="inlineStr">
         <is>
           <t>35292</t>
         </is>
@@ -11842,7 +11872,7 @@
           <t>SMOLEN Michal</t>
         </is>
       </c>
-      <c r="U196" t="inlineStr">
+      <c r="X196" t="inlineStr">
         <is>
           <t>36397</t>
         </is>
@@ -11900,7 +11930,7 @@
           <t>GRIMM Alexander</t>
         </is>
       </c>
-      <c r="U197" t="inlineStr">
+      <c r="X197" t="inlineStr">
         <is>
           <t>35112</t>
         </is>
@@ -11958,7 +11988,7 @@
           <t>BERSINGER Thomas</t>
         </is>
       </c>
-      <c r="U198" t="inlineStr">
+      <c r="X198" t="inlineStr">
         <is>
           <t>35228</t>
         </is>
@@ -12281,7 +12311,7 @@
           <t>SEPRENYI Sara Timea</t>
         </is>
       </c>
-      <c r="U204" t="inlineStr">
+      <c r="X204" t="inlineStr">
         <is>
           <t>52211</t>
         </is>
@@ -12392,7 +12422,7 @@
           <t>HAMER-EVANS Megan</t>
         </is>
       </c>
-      <c r="U206" t="inlineStr">
+      <c r="X206" t="inlineStr">
         <is>
           <t>55138</t>
         </is>
@@ -12450,7 +12480,7 @@
           <t>HUVELIN Flora</t>
         </is>
       </c>
-      <c r="U207" t="inlineStr">
+      <c r="X207" t="inlineStr">
         <is>
           <t>51787</t>
         </is>
@@ -12561,7 +12591,7 @@
           <t>DAVIS Avery</t>
         </is>
       </c>
-      <c r="U209" t="inlineStr">
+      <c r="X209" t="inlineStr">
         <is>
           <t>71336</t>
         </is>
@@ -12619,7 +12649,7 @@
           <t>MARX Alena</t>
         </is>
       </c>
-      <c r="U210" t="inlineStr">
+      <c r="X210" t="inlineStr">
         <is>
           <t>68844</t>
         </is>
@@ -12677,7 +12707,7 @@
           <t>DONNELLY Sage</t>
         </is>
       </c>
-      <c r="U211" t="inlineStr">
+      <c r="X211" t="inlineStr">
         <is>
           <t>60119</t>
         </is>
@@ -12735,7 +12765,7 @@
           <t>BAYLACQ Oceane</t>
         </is>
       </c>
-      <c r="U212" t="inlineStr">
+      <c r="X212" t="inlineStr">
         <is>
           <t>69444</t>
         </is>
@@ -12793,7 +12823,7 @@
           <t>CONLAN Aisling</t>
         </is>
       </c>
-      <c r="U213" t="inlineStr">
+      <c r="X213" t="inlineStr">
         <is>
           <t>35814</t>
         </is>
@@ -12851,7 +12881,7 @@
           <t>OTTEN Maartje</t>
         </is>
       </c>
-      <c r="U214" t="inlineStr">
+      <c r="X214" t="inlineStr">
         <is>
           <t>35337</t>
         </is>
@@ -12909,7 +12939,7 @@
           <t>JAMILI Hind</t>
         </is>
       </c>
-      <c r="U215" t="inlineStr">
+      <c r="X215" t="inlineStr">
         <is>
           <t>43390</t>
         </is>
@@ -12967,7 +12997,7 @@
           <t>WILLIAMS Courtney</t>
         </is>
       </c>
-      <c r="U216" t="inlineStr">
+      <c r="X216" t="inlineStr">
         <is>
           <t>68771</t>
         </is>
@@ -13025,7 +13055,7 @@
           <t>PELLICER CHICA Laura</t>
         </is>
       </c>
-      <c r="U217" t="inlineStr">
+      <c r="X217" t="inlineStr">
         <is>
           <t>43129</t>
         </is>
@@ -13083,7 +13113,7 @@
           <t>MISHIMA Ren</t>
         </is>
       </c>
-      <c r="U218" t="inlineStr">
+      <c r="X218" t="inlineStr">
         <is>
           <t>37757</t>
         </is>
@@ -13300,7 +13330,7 @@
           <t>ITO Yoshika</t>
         </is>
       </c>
-      <c r="U222" t="inlineStr">
+      <c r="X222" t="inlineStr">
         <is>
           <t>36647</t>
         </is>
@@ -13358,7 +13388,7 @@
           <t>MAHEU Florence</t>
         </is>
       </c>
-      <c r="U223" t="inlineStr">
+      <c r="X223" t="inlineStr">
         <is>
           <t>36416</t>
         </is>
@@ -13416,7 +13446,7 @@
           <t>OROKOCKA Viktoria</t>
         </is>
       </c>
-      <c r="U224" t="inlineStr">
+      <c r="X224" t="inlineStr">
         <is>
           <t>35667</t>
         </is>
@@ -13474,7 +13504,7 @@
           <t>MEDON Joanna</t>
         </is>
       </c>
-      <c r="U225" t="inlineStr">
+      <c r="X225" t="inlineStr">
         <is>
           <t>35438</t>
         </is>
@@ -13532,7 +13562,7 @@
           <t>YAZAWA Aki</t>
         </is>
       </c>
-      <c r="U226" t="inlineStr">
+      <c r="X226" t="inlineStr">
         <is>
           <t>36486</t>
         </is>
@@ -13590,7 +13620,7 @@
           <t>WERATSCHNIG Nina</t>
         </is>
       </c>
-      <c r="U227" t="inlineStr">
+      <c r="X227" t="inlineStr">
         <is>
           <t>41614</t>
         </is>
@@ -13648,7 +13678,7 @@
           <t>SABATTINI Chiara</t>
         </is>
       </c>
-      <c r="U228" t="inlineStr">
+      <c r="X228" t="inlineStr">
         <is>
           <t>35219</t>
         </is>
@@ -13706,7 +13736,7 @@
           <t>GIAI PRON Maria Clara</t>
         </is>
       </c>
-      <c r="U229" t="inlineStr">
+      <c r="X229" t="inlineStr">
         <is>
           <t>35218</t>
         </is>
@@ -13764,7 +13794,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U230" t="inlineStr">
+      <c r="X230" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -13822,7 +13852,7 @@
           <t>NOVAK Ajda</t>
         </is>
       </c>
-      <c r="U231" t="inlineStr">
+      <c r="X231" t="inlineStr">
         <is>
           <t>39079</t>
         </is>
@@ -13880,7 +13910,7 @@
           <t>HILGERTOVA Amalie</t>
         </is>
       </c>
-      <c r="U232" t="inlineStr">
+      <c r="X232" t="inlineStr">
         <is>
           <t>36113</t>
         </is>
@@ -13938,7 +13968,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U233" t="inlineStr">
+      <c r="X233" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -13996,7 +14026,7 @@
           <t>ECKHARDT Kate</t>
         </is>
       </c>
-      <c r="U234" t="inlineStr">
+      <c r="X234" t="inlineStr">
         <is>
           <t>44815</t>
         </is>
@@ -14054,7 +14084,7 @@
           <t>NEVARILOVA Kristina</t>
         </is>
       </c>
-      <c r="U235" t="inlineStr">
+      <c r="X235" t="inlineStr">
         <is>
           <t>35467</t>
         </is>
@@ -14112,7 +14142,7 @@
           <t>WEGMAN Martina</t>
         </is>
       </c>
-      <c r="U236" t="inlineStr">
+      <c r="X236" t="inlineStr">
         <is>
           <t>35345</t>
         </is>
@@ -14223,7 +14253,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U238" t="inlineStr">
+      <c r="X238" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -14281,7 +14311,7 @@
           <t>TROMPETER Caroline</t>
         </is>
       </c>
-      <c r="U239" t="inlineStr">
+      <c r="X239" t="inlineStr">
         <is>
           <t>39167</t>
         </is>
@@ -14339,7 +14369,7 @@
           <t>ZWOLINSKA Klaudia</t>
         </is>
       </c>
-      <c r="U240" t="inlineStr">
+      <c r="X240" t="inlineStr">
         <is>
           <t>42027</t>
         </is>
@@ -14397,7 +14427,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U241" t="inlineStr">
+      <c r="X241" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -14455,7 +14485,7 @@
           <t>FRITSCHE Lisa</t>
         </is>
       </c>
-      <c r="U242" t="inlineStr">
+      <c r="X242" t="inlineStr">
         <is>
           <t>39883</t>
         </is>
@@ -14513,7 +14543,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U243" t="inlineStr">
+      <c r="X243" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -14571,7 +14601,7 @@
           <t>LEITNER Lisa</t>
         </is>
       </c>
-      <c r="U244" t="inlineStr">
+      <c r="X244" t="inlineStr">
         <is>
           <t>35305</t>
         </is>
@@ -14629,7 +14659,7 @@
           <t>LAFONT Marie-Zelia</t>
         </is>
       </c>
-      <c r="U245" t="inlineStr">
+      <c r="X245" t="inlineStr">
         <is>
           <t>35374</t>
         </is>
@@ -14687,7 +14717,7 @@
           <t>KRAGELJ Ursa</t>
         </is>
       </c>
-      <c r="U246" t="inlineStr">
+      <c r="X246" t="inlineStr">
         <is>
           <t>36264</t>
         </is>
@@ -14745,7 +14775,7 @@
           <t>HORN Stefanie</t>
         </is>
       </c>
-      <c r="U247" t="inlineStr">
+      <c r="X247" t="inlineStr">
         <is>
           <t>38417</t>
         </is>
@@ -14803,7 +14833,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U248" t="inlineStr">
+      <c r="X248" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -14861,7 +14891,7 @@
           <t>SCHORNBERG Jasmin</t>
         </is>
       </c>
-      <c r="U249" t="inlineStr">
+      <c r="X249" t="inlineStr">
         <is>
           <t>35206</t>
         </is>
@@ -14919,7 +14949,7 @@
           <t>KUDEJOVA Katerina</t>
         </is>
       </c>
-      <c r="U250" t="inlineStr">
+      <c r="X250" t="inlineStr">
         <is>
           <t>35034</t>
         </is>
@@ -14977,7 +15007,7 @@
           <t>DUKATOVA Jana</t>
         </is>
       </c>
-      <c r="U251" t="inlineStr">
+      <c r="X251" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
@@ -15035,7 +15065,7 @@
           <t>KUHNLE Corinna</t>
         </is>
       </c>
-      <c r="U252" t="inlineStr">
+      <c r="X252" t="inlineStr">
         <is>
           <t>35282</t>
         </is>
@@ -15093,7 +15123,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U253" t="inlineStr">
+      <c r="X253" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -15151,7 +15181,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U254" t="inlineStr">
+      <c r="X254" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -15209,7 +15239,7 @@
           <t>MAJERCZAK Grzegorz</t>
         </is>
       </c>
-      <c r="U255" t="inlineStr">
+      <c r="X255" t="inlineStr">
         <is>
           <t>35086</t>
         </is>
@@ -15267,7 +15297,7 @@
           <t>ROISIN Theo</t>
         </is>
       </c>
-      <c r="U256" t="inlineStr">
+      <c r="X256" t="inlineStr">
         <is>
           <t>69010</t>
         </is>
@@ -15325,7 +15355,7 @@
           <t>ALVARENGA Frederico</t>
         </is>
       </c>
-      <c r="U257" t="inlineStr">
+      <c r="X257" t="inlineStr">
         <is>
           <t>71976</t>
         </is>
@@ -15383,7 +15413,7 @@
           <t>SEEMANN Eloi</t>
         </is>
       </c>
-      <c r="U258" t="inlineStr">
+      <c r="X258" t="inlineStr">
         <is>
           <t>44378</t>
         </is>
@@ -15441,7 +15471,7 @@
           <t>PALMCRANTZ Ludwig</t>
         </is>
       </c>
-      <c r="U259" t="inlineStr">
+      <c r="X259" t="inlineStr">
         <is>
           <t>60179</t>
         </is>
@@ -15499,7 +15529,7 @@
           <t>TANIGUCHI Kazuya</t>
         </is>
       </c>
-      <c r="U260" t="inlineStr">
+      <c r="X260" t="inlineStr">
         <is>
           <t>39699</t>
         </is>
@@ -15557,7 +15587,7 @@
           <t>ABBOTT Thomas</t>
         </is>
       </c>
-      <c r="U261" t="inlineStr">
+      <c r="X261" t="inlineStr">
         <is>
           <t>36514</t>
         </is>
@@ -15615,7 +15645,7 @@
           <t>ROISIN Lucas</t>
         </is>
       </c>
-      <c r="U262" t="inlineStr">
+      <c r="X262" t="inlineStr">
         <is>
           <t>55580</t>
         </is>
@@ -15673,7 +15703,7 @@
           <t>KOLOMANSKI Michal</t>
         </is>
       </c>
-      <c r="U263" t="inlineStr">
+      <c r="X263" t="inlineStr">
         <is>
           <t>35091</t>
         </is>
@@ -15731,7 +15761,7 @@
           <t>DOBY Mathieu</t>
         </is>
       </c>
-      <c r="U264" t="inlineStr">
+      <c r="X264" t="inlineStr">
         <is>
           <t>35292</t>
         </is>
@@ -15789,7 +15819,7 @@
           <t>LONG Tren</t>
         </is>
       </c>
-      <c r="U265" t="inlineStr">
+      <c r="X265" t="inlineStr">
         <is>
           <t>57124</t>
         </is>
@@ -15847,7 +15877,7 @@
           <t>HIGGINS Shaun</t>
         </is>
       </c>
-      <c r="U266" t="inlineStr">
+      <c r="X266" t="inlineStr">
         <is>
           <t>36655</t>
         </is>
@@ -15905,7 +15935,7 @@
           <t>SMEDLEY Liam</t>
         </is>
       </c>
-      <c r="U267" t="inlineStr">
+      <c r="X267" t="inlineStr">
         <is>
           <t>36517</t>
         </is>
@@ -15963,7 +15993,7 @@
           <t>COCHRANE Jake</t>
         </is>
       </c>
-      <c r="U268" t="inlineStr">
+      <c r="X268" t="inlineStr">
         <is>
           <t>60124</t>
         </is>
@@ -16021,7 +16051,7 @@
           <t>WERRO Simon</t>
         </is>
       </c>
-      <c r="U269" t="inlineStr">
+      <c r="X269" t="inlineStr">
         <is>
           <t>35424</t>
         </is>
@@ -16132,7 +16162,7 @@
           <t>POMEROY Spencer</t>
         </is>
       </c>
-      <c r="U271" t="inlineStr">
+      <c r="X271" t="inlineStr">
         <is>
           <t>57783</t>
         </is>
@@ -16190,7 +16220,7 @@
           <t>LHOTA Matyas</t>
         </is>
       </c>
-      <c r="U272" t="inlineStr">
+      <c r="X272" t="inlineStr">
         <is>
           <t>51872</t>
         </is>
@@ -16301,7 +16331,7 @@
           <t>GIBB Benjamin</t>
         </is>
       </c>
-      <c r="U274" t="inlineStr">
+      <c r="X274" t="inlineStr">
         <is>
           <t>36711</t>
         </is>
@@ -16359,7 +16389,7 @@
           <t>CORREA Charles</t>
         </is>
       </c>
-      <c r="U275" t="inlineStr">
+      <c r="X275" t="inlineStr">
         <is>
           <t>38018</t>
         </is>
@@ -16417,7 +16447,7 @@
           <t>WATKINS Daniel</t>
         </is>
       </c>
-      <c r="U276" t="inlineStr">
+      <c r="X276" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -16475,7 +16505,7 @@
           <t>CARTER Tristan</t>
         </is>
       </c>
-      <c r="U277" t="inlineStr">
+      <c r="X277" t="inlineStr">
         <is>
           <t>51890</t>
         </is>
@@ -16533,7 +16563,7 @@
           <t>BORGES Felipe</t>
         </is>
       </c>
-      <c r="U278" t="inlineStr">
+      <c r="X278" t="inlineStr">
         <is>
           <t>38012</t>
         </is>
@@ -16591,7 +16621,7 @@
           <t>BORROWS Ian</t>
         </is>
       </c>
-      <c r="U279" t="inlineStr">
+      <c r="X279" t="inlineStr">
         <is>
           <t>36534</t>
         </is>
@@ -16649,7 +16679,7 @@
           <t>LE RUYET Edern</t>
         </is>
       </c>
-      <c r="U280" t="inlineStr">
+      <c r="X280" t="inlineStr">
         <is>
           <t>35379</t>
         </is>
@@ -16707,7 +16737,7 @@
           <t>CIPRESSI Stefano</t>
         </is>
       </c>
-      <c r="U281" t="inlineStr">
+      <c r="X281" t="inlineStr">
         <is>
           <t>35495</t>
         </is>
@@ -16765,7 +16795,7 @@
           <t>LOKKEN Zachary</t>
         </is>
       </c>
-      <c r="U282" t="inlineStr">
+      <c r="X282" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
@@ -16823,7 +16853,7 @@
           <t>JEGOU Liam</t>
         </is>
       </c>
-      <c r="U283" t="inlineStr">
+      <c r="X283" t="inlineStr">
         <is>
           <t>35820</t>
         </is>
@@ -16881,7 +16911,7 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U284" t="inlineStr">
+      <c r="X284" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -16939,7 +16969,7 @@
           <t>CHALOUPKA Vaclav</t>
         </is>
       </c>
-      <c r="U285" t="inlineStr">
+      <c r="X285" t="inlineStr">
         <is>
           <t>51648</t>
         </is>
@@ -16997,7 +17027,7 @@
           <t>SMEDLEY Cameron</t>
         </is>
       </c>
-      <c r="U286" t="inlineStr">
+      <c r="X286" t="inlineStr">
         <is>
           <t>35543</t>
         </is>
@@ -17055,7 +17085,7 @@
           <t>COLAZINGARI Roberto</t>
         </is>
       </c>
-      <c r="U287" t="inlineStr">
+      <c r="X287" t="inlineStr">
         <is>
           <t>35223</t>
         </is>
@@ -17113,7 +17143,7 @@
           <t>IVALDI Raffaello</t>
         </is>
       </c>
-      <c r="U288" t="inlineStr">
+      <c r="X288" t="inlineStr">
         <is>
           <t>35227</t>
         </is>
@@ -17171,7 +17201,7 @@
           <t>JANE Michal</t>
         </is>
       </c>
-      <c r="U289" t="inlineStr">
+      <c r="X289" t="inlineStr">
         <is>
           <t>35059</t>
         </is>
@@ -17229,7 +17259,7 @@
           <t>BADURA Jergus</t>
         </is>
       </c>
-      <c r="U290" t="inlineStr">
+      <c r="X290" t="inlineStr">
         <is>
           <t>68767</t>
         </is>
@@ -17287,7 +17317,7 @@
           <t>LENARCIC Jure</t>
         </is>
       </c>
-      <c r="U291" t="inlineStr">
+      <c r="X291" t="inlineStr">
         <is>
           <t>36259</t>
         </is>
@@ -17345,7 +17375,7 @@
           <t>HEDWIG Grzegorz</t>
         </is>
       </c>
-      <c r="U292" t="inlineStr">
+      <c r="X292" t="inlineStr">
         <is>
           <t>35465</t>
         </is>
@@ -17403,7 +17433,7 @@
           <t>THOMAS Martin</t>
         </is>
       </c>
-      <c r="U293" t="inlineStr">
+      <c r="X293" t="inlineStr">
         <is>
           <t>35412</t>
         </is>
@@ -17461,7 +17491,7 @@
           <t>BOZIC Luka</t>
         </is>
       </c>
-      <c r="U294" t="inlineStr">
+      <c r="X294" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
@@ -17519,7 +17549,7 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U295" t="inlineStr">
+      <c r="X295" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -17577,7 +17607,7 @@
           <t>KOECHLIN Thomas</t>
         </is>
       </c>
-      <c r="U296" t="inlineStr">
+      <c r="X296" t="inlineStr">
         <is>
           <t>35419</t>
         </is>
@@ -17635,7 +17665,7 @@
           <t>BERCIC Anze</t>
         </is>
       </c>
-      <c r="U297" t="inlineStr">
+      <c r="X297" t="inlineStr">
         <is>
           <t>36253</t>
         </is>
@@ -17693,7 +17723,7 @@
           <t>ROHAN Lukas</t>
         </is>
       </c>
-      <c r="U298" t="inlineStr">
+      <c r="X298" t="inlineStr">
         <is>
           <t>36114</t>
         </is>
@@ -17751,7 +17781,7 @@
           <t>MARTIKAN Michal</t>
         </is>
       </c>
-      <c r="U299" t="inlineStr">
+      <c r="X299" t="inlineStr">
         <is>
           <t>35365</t>
         </is>
@@ -17809,7 +17839,7 @@
           <t>ANTON Franz</t>
         </is>
       </c>
-      <c r="U300" t="inlineStr">
+      <c r="X300" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
@@ -17867,7 +17897,7 @@
           <t>TASIADIS Sideris</t>
         </is>
       </c>
-      <c r="U301" t="inlineStr">
+      <c r="X301" t="inlineStr">
         <is>
           <t>35135</t>
         </is>
@@ -17925,7 +17955,7 @@
           <t>SLAFKOVSKY Alexander</t>
         </is>
       </c>
-      <c r="U302" t="inlineStr">
+      <c r="X302" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
@@ -17983,7 +18013,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U303" t="inlineStr">
+      <c r="X303" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -18094,7 +18124,7 @@
           <t>SEPRENYI Sara Timea</t>
         </is>
       </c>
-      <c r="U305" t="inlineStr">
+      <c r="X305" t="inlineStr">
         <is>
           <t>52211</t>
         </is>
@@ -18205,7 +18235,7 @@
           <t>HAMER-EVANS Megan</t>
         </is>
       </c>
-      <c r="U307" t="inlineStr">
+      <c r="X307" t="inlineStr">
         <is>
           <t>55138</t>
         </is>
@@ -18263,7 +18293,7 @@
           <t>HUVELIN Flora</t>
         </is>
       </c>
-      <c r="U308" t="inlineStr">
+      <c r="X308" t="inlineStr">
         <is>
           <t>51787</t>
         </is>
@@ -18374,7 +18404,7 @@
           <t>DAVIS Avery</t>
         </is>
       </c>
-      <c r="U310" t="inlineStr">
+      <c r="X310" t="inlineStr">
         <is>
           <t>71336</t>
         </is>
@@ -18432,7 +18462,7 @@
           <t>MARX Alena</t>
         </is>
       </c>
-      <c r="U311" t="inlineStr">
+      <c r="X311" t="inlineStr">
         <is>
           <t>68844</t>
         </is>
@@ -18490,7 +18520,7 @@
           <t>DONNELLY Sage</t>
         </is>
       </c>
-      <c r="U312" t="inlineStr">
+      <c r="X312" t="inlineStr">
         <is>
           <t>60119</t>
         </is>
@@ -18548,7 +18578,7 @@
           <t>BAYLACQ Oceane</t>
         </is>
       </c>
-      <c r="U313" t="inlineStr">
+      <c r="X313" t="inlineStr">
         <is>
           <t>69444</t>
         </is>
@@ -18606,7 +18636,7 @@
           <t>CONLAN Aisling</t>
         </is>
       </c>
-      <c r="U314" t="inlineStr">
+      <c r="X314" t="inlineStr">
         <is>
           <t>35814</t>
         </is>
@@ -18664,7 +18694,7 @@
           <t>OTTEN Maartje</t>
         </is>
       </c>
-      <c r="U315" t="inlineStr">
+      <c r="X315" t="inlineStr">
         <is>
           <t>35337</t>
         </is>
@@ -18722,7 +18752,7 @@
           <t>JAMILI Hind</t>
         </is>
       </c>
-      <c r="U316" t="inlineStr">
+      <c r="X316" t="inlineStr">
         <is>
           <t>43390</t>
         </is>
@@ -18780,7 +18810,7 @@
           <t>WILLIAMS Courtney</t>
         </is>
       </c>
-      <c r="U317" t="inlineStr">
+      <c r="X317" t="inlineStr">
         <is>
           <t>68771</t>
         </is>
@@ -18838,7 +18868,7 @@
           <t>PELLICER CHICA Laura</t>
         </is>
       </c>
-      <c r="U318" t="inlineStr">
+      <c r="X318" t="inlineStr">
         <is>
           <t>43129</t>
         </is>
@@ -18896,7 +18926,7 @@
           <t>MISHIMA Ren</t>
         </is>
       </c>
-      <c r="U319" t="inlineStr">
+      <c r="X319" t="inlineStr">
         <is>
           <t>37757</t>
         </is>
@@ -19060,7 +19090,7 @@
           <t>ITO Yoshika</t>
         </is>
       </c>
-      <c r="U322" t="inlineStr">
+      <c r="X322" t="inlineStr">
         <is>
           <t>36647</t>
         </is>
@@ -19118,7 +19148,7 @@
           <t>MAHEU Florence</t>
         </is>
       </c>
-      <c r="U323" t="inlineStr">
+      <c r="X323" t="inlineStr">
         <is>
           <t>36416</t>
         </is>
@@ -19176,7 +19206,7 @@
           <t>OROKOCKA Viktoria</t>
         </is>
       </c>
-      <c r="U324" t="inlineStr">
+      <c r="X324" t="inlineStr">
         <is>
           <t>35667</t>
         </is>
@@ -19234,7 +19264,7 @@
           <t>MEDON Joanna</t>
         </is>
       </c>
-      <c r="U325" t="inlineStr">
+      <c r="X325" t="inlineStr">
         <is>
           <t>35438</t>
         </is>
@@ -19292,7 +19322,7 @@
           <t>YAZAWA Aki</t>
         </is>
       </c>
-      <c r="U326" t="inlineStr">
+      <c r="X326" t="inlineStr">
         <is>
           <t>36486</t>
         </is>
@@ -19350,7 +19380,7 @@
           <t>WERATSCHNIG Nina</t>
         </is>
       </c>
-      <c r="U327" t="inlineStr">
+      <c r="X327" t="inlineStr">
         <is>
           <t>41614</t>
         </is>
@@ -19408,7 +19438,7 @@
           <t>SABATTINI Chiara</t>
         </is>
       </c>
-      <c r="U328" t="inlineStr">
+      <c r="X328" t="inlineStr">
         <is>
           <t>35219</t>
         </is>
@@ -19466,7 +19496,7 @@
           <t>GIAI PRON Maria Clara</t>
         </is>
       </c>
-      <c r="U329" t="inlineStr">
+      <c r="X329" t="inlineStr">
         <is>
           <t>35218</t>
         </is>
@@ -19524,7 +19554,7 @@
           <t>NOVAK Ajda</t>
         </is>
       </c>
-      <c r="U330" t="inlineStr">
+      <c r="X330" t="inlineStr">
         <is>
           <t>39079</t>
         </is>
@@ -19582,7 +19612,7 @@
           <t>NEVARILOVA Kristina</t>
         </is>
       </c>
-      <c r="U331" t="inlineStr">
+      <c r="X331" t="inlineStr">
         <is>
           <t>35467</t>
         </is>
@@ -19640,7 +19670,7 @@
           <t>WEGMAN Martina</t>
         </is>
       </c>
-      <c r="U332" t="inlineStr">
+      <c r="X332" t="inlineStr">
         <is>
           <t>35345</t>
         </is>
@@ -19751,7 +19781,7 @@
           <t>TROMPETER Caroline</t>
         </is>
       </c>
-      <c r="U334" t="inlineStr">
+      <c r="X334" t="inlineStr">
         <is>
           <t>39167</t>
         </is>
@@ -19809,7 +19839,7 @@
           <t>ZWOLINSKA Klaudia</t>
         </is>
       </c>
-      <c r="U335" t="inlineStr">
+      <c r="X335" t="inlineStr">
         <is>
           <t>42027</t>
         </is>
@@ -19867,7 +19897,7 @@
           <t>FRITSCHE Lisa</t>
         </is>
       </c>
-      <c r="U336" t="inlineStr">
+      <c r="X336" t="inlineStr">
         <is>
           <t>39883</t>
         </is>
@@ -19925,7 +19955,7 @@
           <t>MAJERCZAK Grzegorz</t>
         </is>
       </c>
-      <c r="U337" t="inlineStr">
+      <c r="X337" t="inlineStr">
         <is>
           <t>35086</t>
         </is>
@@ -19983,7 +20013,7 @@
           <t>ROISIN Theo</t>
         </is>
       </c>
-      <c r="U338" t="inlineStr">
+      <c r="X338" t="inlineStr">
         <is>
           <t>69010</t>
         </is>
@@ -20041,7 +20071,7 @@
           <t>ALVARENGA Frederico</t>
         </is>
       </c>
-      <c r="U339" t="inlineStr">
+      <c r="X339" t="inlineStr">
         <is>
           <t>71976</t>
         </is>
@@ -20099,7 +20129,7 @@
           <t>SEEMANN Eloi</t>
         </is>
       </c>
-      <c r="U340" t="inlineStr">
+      <c r="X340" t="inlineStr">
         <is>
           <t>44378</t>
         </is>
@@ -20157,7 +20187,7 @@
           <t>PALMCRANTZ Ludwig</t>
         </is>
       </c>
-      <c r="U341" t="inlineStr">
+      <c r="X341" t="inlineStr">
         <is>
           <t>60179</t>
         </is>
@@ -20215,7 +20245,7 @@
           <t>TANIGUCHI Kazuya</t>
         </is>
       </c>
-      <c r="U342" t="inlineStr">
+      <c r="X342" t="inlineStr">
         <is>
           <t>39699</t>
         </is>
@@ -20273,7 +20303,7 @@
           <t>ABBOTT Thomas</t>
         </is>
       </c>
-      <c r="U343" t="inlineStr">
+      <c r="X343" t="inlineStr">
         <is>
           <t>36514</t>
         </is>
@@ -20331,7 +20361,7 @@
           <t>ROISIN Lucas</t>
         </is>
       </c>
-      <c r="U344" t="inlineStr">
+      <c r="X344" t="inlineStr">
         <is>
           <t>55580</t>
         </is>
@@ -20389,7 +20419,7 @@
           <t>KOLOMANSKI Michal</t>
         </is>
       </c>
-      <c r="U345" t="inlineStr">
+      <c r="X345" t="inlineStr">
         <is>
           <t>35091</t>
         </is>
@@ -20447,7 +20477,7 @@
           <t>DOBY Mathieu</t>
         </is>
       </c>
-      <c r="U346" t="inlineStr">
+      <c r="X346" t="inlineStr">
         <is>
           <t>35292</t>
         </is>
@@ -20505,7 +20535,7 @@
           <t>LONG Tren</t>
         </is>
       </c>
-      <c r="U347" t="inlineStr">
+      <c r="X347" t="inlineStr">
         <is>
           <t>57124</t>
         </is>
@@ -20563,7 +20593,7 @@
           <t>HIGGINS Shaun</t>
         </is>
       </c>
-      <c r="U348" t="inlineStr">
+      <c r="X348" t="inlineStr">
         <is>
           <t>36655</t>
         </is>
@@ -20621,7 +20651,7 @@
           <t>SMEDLEY Liam</t>
         </is>
       </c>
-      <c r="U349" t="inlineStr">
+      <c r="X349" t="inlineStr">
         <is>
           <t>36517</t>
         </is>
@@ -20679,7 +20709,7 @@
           <t>COCHRANE Jake</t>
         </is>
       </c>
-      <c r="U350" t="inlineStr">
+      <c r="X350" t="inlineStr">
         <is>
           <t>60124</t>
         </is>
@@ -20737,7 +20767,7 @@
           <t>WERRO Simon</t>
         </is>
       </c>
-      <c r="U351" t="inlineStr">
+      <c r="X351" t="inlineStr">
         <is>
           <t>35424</t>
         </is>
@@ -20795,7 +20825,7 @@
           <t>POMEROY Spencer</t>
         </is>
       </c>
-      <c r="U352" t="inlineStr">
+      <c r="X352" t="inlineStr">
         <is>
           <t>57783</t>
         </is>
@@ -20853,7 +20883,7 @@
           <t>LHOTA Matyas</t>
         </is>
       </c>
-      <c r="U353" t="inlineStr">
+      <c r="X353" t="inlineStr">
         <is>
           <t>51872</t>
         </is>
@@ -20911,7 +20941,7 @@
           <t>GIBB Benjamin</t>
         </is>
       </c>
-      <c r="U354" t="inlineStr">
+      <c r="X354" t="inlineStr">
         <is>
           <t>36711</t>
         </is>
@@ -20969,7 +20999,7 @@
           <t>CORREA Charles</t>
         </is>
       </c>
-      <c r="U355" t="inlineStr">
+      <c r="X355" t="inlineStr">
         <is>
           <t>38018</t>
         </is>
@@ -21027,7 +21057,7 @@
           <t>CARTER Tristan</t>
         </is>
       </c>
-      <c r="U356" t="inlineStr">
+      <c r="X356" t="inlineStr">
         <is>
           <t>51890</t>
         </is>
@@ -21085,7 +21115,7 @@
           <t>BORGES Felipe</t>
         </is>
       </c>
-      <c r="U357" t="inlineStr">
+      <c r="X357" t="inlineStr">
         <is>
           <t>38012</t>
         </is>
@@ -21143,7 +21173,7 @@
           <t>BORROWS Ian</t>
         </is>
       </c>
-      <c r="U358" t="inlineStr">
+      <c r="X358" t="inlineStr">
         <is>
           <t>36534</t>
         </is>
@@ -21201,7 +21231,7 @@
           <t>LE RUYET Edern</t>
         </is>
       </c>
-      <c r="U359" t="inlineStr">
+      <c r="X359" t="inlineStr">
         <is>
           <t>35379</t>
         </is>
@@ -21259,7 +21289,7 @@
           <t>LOKKEN Zachary</t>
         </is>
       </c>
-      <c r="U360" t="inlineStr">
+      <c r="X360" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
@@ -21317,7 +21347,7 @@
           <t>JEGOU Liam</t>
         </is>
       </c>
-      <c r="U361" t="inlineStr">
+      <c r="X361" t="inlineStr">
         <is>
           <t>35820</t>
         </is>
@@ -21375,7 +21405,7 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U362" t="inlineStr">
+      <c r="X362" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -21433,7 +21463,7 @@
           <t>JANE Michal</t>
         </is>
       </c>
-      <c r="U363" t="inlineStr">
+      <c r="X363" t="inlineStr">
         <is>
           <t>35059</t>
         </is>
@@ -21491,7 +21521,7 @@
           <t>BADURA Jergus</t>
         </is>
       </c>
-      <c r="U364" t="inlineStr">
+      <c r="X364" t="inlineStr">
         <is>
           <t>68767</t>
         </is>
@@ -21549,7 +21579,7 @@
           <t>LENARCIC Jure</t>
         </is>
       </c>
-      <c r="U365" t="inlineStr">
+      <c r="X365" t="inlineStr">
         <is>
           <t>36259</t>
         </is>
@@ -21607,7 +21637,7 @@
           <t>ROHAN Lukas</t>
         </is>
       </c>
-      <c r="U366" t="inlineStr">
+      <c r="X366" t="inlineStr">
         <is>
           <t>36114</t>
         </is>
@@ -21882,12 +21912,12 @@
           <t>BECKER Thomas</t>
         </is>
       </c>
-      <c r="U371" t="inlineStr">
+      <c r="X371" t="inlineStr">
         <is>
           <t>35139</t>
         </is>
       </c>
-      <c r="V371" t="inlineStr">
+      <c r="Y371" t="inlineStr">
         <is>
           <t>35143</t>
         </is>
@@ -21950,12 +21980,12 @@
           <t>TILLARD Pierre-Antoine</t>
         </is>
       </c>
-      <c r="U372" t="inlineStr">
+      <c r="X372" t="inlineStr">
         <is>
           <t>35379</t>
         </is>
       </c>
-      <c r="V372" t="inlineStr">
+      <c r="Y372" t="inlineStr">
         <is>
           <t>35413</t>
         </is>
@@ -22018,12 +22048,12 @@
           <t>VRZAN Jakub</t>
         </is>
       </c>
-      <c r="U373" t="inlineStr">
+      <c r="X373" t="inlineStr">
         <is>
           <t>35042</t>
         </is>
       </c>
-      <c r="V373" t="inlineStr">
+      <c r="Y373" t="inlineStr">
         <is>
           <t>35043</t>
         </is>
@@ -22086,12 +22116,12 @@
           <t>HEGER Tomas</t>
         </is>
       </c>
-      <c r="U374" t="inlineStr">
+      <c r="X374" t="inlineStr">
         <is>
           <t>68872</t>
         </is>
       </c>
-      <c r="V374" t="inlineStr">
+      <c r="Y374" t="inlineStr">
         <is>
           <t>42007</t>
         </is>
@@ -22154,12 +22184,12 @@
           <t>GEWISSLER Matus</t>
         </is>
       </c>
-      <c r="U375" t="inlineStr">
+      <c r="X375" t="inlineStr">
         <is>
           <t>39248</t>
         </is>
       </c>
-      <c r="V375" t="inlineStr">
+      <c r="Y375" t="inlineStr">
         <is>
           <t>39249</t>
         </is>
@@ -22222,12 +22252,12 @@
           <t>QUERCI Alberto</t>
         </is>
       </c>
-      <c r="U376" t="inlineStr">
+      <c r="X376" t="inlineStr">
         <is>
           <t>39904</t>
         </is>
       </c>
-      <c r="V376" t="inlineStr">
+      <c r="Y376" t="inlineStr">
         <is>
           <t>39906</t>
         </is>
@@ -22290,12 +22320,12 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U377" t="inlineStr">
+      <c r="X377" t="inlineStr">
         <is>
           <t>35145</t>
         </is>
       </c>
-      <c r="V377" t="inlineStr">
+      <c r="Y377" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -22358,12 +22388,12 @@
           <t>WERRO Simon</t>
         </is>
       </c>
-      <c r="U378" t="inlineStr">
+      <c r="X378" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
       </c>
-      <c r="V378" t="inlineStr">
+      <c r="Y378" t="inlineStr">
         <is>
           <t>35424</t>
         </is>
@@ -22426,12 +22456,12 @@
           <t>BATIK Jan</t>
         </is>
       </c>
-      <c r="U379" t="inlineStr">
+      <c r="X379" t="inlineStr">
         <is>
           <t>35368</t>
         </is>
       </c>
-      <c r="V379" t="inlineStr">
+      <c r="Y379" t="inlineStr">
         <is>
           <t>35367</t>
         </is>
@@ -22494,12 +22524,12 @@
           <t>PECHE Matthieu</t>
         </is>
       </c>
-      <c r="U380" t="inlineStr">
+      <c r="X380" t="inlineStr">
         <is>
           <t>35350</t>
         </is>
       </c>
-      <c r="V380" t="inlineStr">
+      <c r="Y380" t="inlineStr">
         <is>
           <t>35400</t>
         </is>
@@ -22562,12 +22592,12 @@
           <t>HOCHSCHORNER Peter</t>
         </is>
       </c>
-      <c r="U381" t="inlineStr">
+      <c r="X381" t="inlineStr">
         <is>
           <t>35356</t>
         </is>
       </c>
-      <c r="V381" t="inlineStr">
+      <c r="Y381" t="inlineStr">
         <is>
           <t>35357</t>
         </is>
@@ -22630,12 +22660,12 @@
           <t>FERRARI Niccolo</t>
         </is>
       </c>
-      <c r="U382" t="inlineStr">
+      <c r="X382" t="inlineStr">
         <is>
           <t>35497</t>
         </is>
       </c>
-      <c r="V382" t="inlineStr">
+      <c r="Y382" t="inlineStr">
         <is>
           <t>35498</t>
         </is>
@@ -22698,12 +22728,12 @@
           <t>SKANTAR Peter</t>
         </is>
       </c>
-      <c r="U383" t="inlineStr">
+      <c r="X383" t="inlineStr">
         <is>
           <t>35360</t>
         </is>
       </c>
-      <c r="V383" t="inlineStr">
+      <c r="Y383" t="inlineStr">
         <is>
           <t>35361</t>
         </is>
@@ -22766,12 +22796,12 @@
           <t>CAILHOL Hugo</t>
         </is>
       </c>
-      <c r="U384" t="inlineStr">
+      <c r="X384" t="inlineStr">
         <is>
           <t>35476</t>
         </is>
       </c>
-      <c r="V384" t="inlineStr">
+      <c r="Y384" t="inlineStr">
         <is>
           <t>35491</t>
         </is>
@@ -22834,12 +22864,12 @@
           <t>BISO Hugo</t>
         </is>
       </c>
-      <c r="U385" t="inlineStr">
+      <c r="X385" t="inlineStr">
         <is>
           <t>35403</t>
         </is>
       </c>
-      <c r="V385" t="inlineStr">
+      <c r="Y385" t="inlineStr">
         <is>
           <t>35229</t>
         </is>
@@ -22902,12 +22932,12 @@
           <t>SINDLER Marek</t>
         </is>
       </c>
-      <c r="U386" t="inlineStr">
+      <c r="X386" t="inlineStr">
         <is>
           <t>35062</t>
         </is>
       </c>
-      <c r="V386" t="inlineStr">
+      <c r="Y386" t="inlineStr">
         <is>
           <t>35063</t>
         </is>
@@ -22965,7 +22995,7 @@
           <t>DIESKOVA Eva</t>
         </is>
       </c>
-      <c r="U387" t="inlineStr">
+      <c r="X387" t="inlineStr">
         <is>
           <t>71639</t>
         </is>
@@ -23023,7 +23053,7 @@
           <t>KOZOROG Alja</t>
         </is>
       </c>
-      <c r="U388" t="inlineStr">
+      <c r="X388" t="inlineStr">
         <is>
           <t>39986</t>
         </is>
@@ -23081,7 +23111,7 @@
           <t>HERZOG Andrea</t>
         </is>
       </c>
-      <c r="U389" t="inlineStr">
+      <c r="X389" t="inlineStr">
         <is>
           <t>55099</t>
         </is>
@@ -23139,7 +23169,7 @@
           <t>OHMAYER Birgit</t>
         </is>
       </c>
-      <c r="U390" t="inlineStr">
+      <c r="X390" t="inlineStr">
         <is>
           <t>39157</t>
         </is>
@@ -23250,7 +23280,7 @@
           <t>BIZJAK Nina</t>
         </is>
       </c>
-      <c r="U392" t="inlineStr">
+      <c r="X392" t="inlineStr">
         <is>
           <t>39984</t>
         </is>
@@ -23308,7 +23338,7 @@
           <t>STOECKLIN Lena</t>
         </is>
       </c>
-      <c r="U393" t="inlineStr">
+      <c r="X393" t="inlineStr">
         <is>
           <t>35822</t>
         </is>
@@ -23366,7 +23396,7 @@
           <t>FORROW Bethan</t>
         </is>
       </c>
-      <c r="U394" t="inlineStr">
+      <c r="X394" t="inlineStr">
         <is>
           <t>69065</t>
         </is>
@@ -23424,7 +23454,7 @@
           <t>OLAZABAL Klara</t>
         </is>
       </c>
-      <c r="U395" t="inlineStr">
+      <c r="X395" t="inlineStr">
         <is>
           <t>43985</t>
         </is>
@@ -23482,7 +23512,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U396" t="inlineStr">
+      <c r="X396" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -23540,7 +23570,7 @@
           <t>HAVLICKOVA Katerina</t>
         </is>
       </c>
-      <c r="U397" t="inlineStr">
+      <c r="X397" t="inlineStr">
         <is>
           <t>35048</t>
         </is>
@@ -23598,7 +23628,7 @@
           <t>SPICER Phoebe</t>
         </is>
       </c>
-      <c r="U398" t="inlineStr">
+      <c r="X398" t="inlineStr">
         <is>
           <t>75827</t>
         </is>
@@ -23656,7 +23686,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U399" t="inlineStr">
+      <c r="X399" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -23714,7 +23744,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U400" t="inlineStr">
+      <c r="X400" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -23772,7 +23802,7 @@
           <t>BORGHI Elena</t>
         </is>
       </c>
-      <c r="U401" t="inlineStr">
+      <c r="X401" t="inlineStr">
         <is>
           <t>75493</t>
         </is>
@@ -23830,7 +23860,7 @@
           <t>PRIOUX Lucie</t>
         </is>
       </c>
-      <c r="U402" t="inlineStr">
+      <c r="X402" t="inlineStr">
         <is>
           <t>42984</t>
         </is>
@@ -23888,7 +23918,7 @@
           <t>JANCOVA Monika</t>
         </is>
       </c>
-      <c r="U403" t="inlineStr">
+      <c r="X403" t="inlineStr">
         <is>
           <t>36015</t>
         </is>
@@ -23946,7 +23976,7 @@
           <t>TIXIER Cecile</t>
         </is>
       </c>
-      <c r="U404" t="inlineStr">
+      <c r="X404" t="inlineStr">
         <is>
           <t>35687</t>
         </is>
@@ -24004,7 +24034,7 @@
           <t>JACQUET Claire</t>
         </is>
       </c>
-      <c r="U405" t="inlineStr">
+      <c r="X405" t="inlineStr">
         <is>
           <t>35684</t>
         </is>
@@ -24062,7 +24092,7 @@
           <t>STANOVSKA Sona</t>
         </is>
       </c>
-      <c r="U406" t="inlineStr">
+      <c r="X406" t="inlineStr">
         <is>
           <t>51647</t>
         </is>
@@ -24120,7 +24150,7 @@
           <t>MACEKOVA Simona</t>
         </is>
       </c>
-      <c r="U407" t="inlineStr">
+      <c r="X407" t="inlineStr">
         <is>
           <t>45153</t>
         </is>
@@ -24231,7 +24261,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U409" t="inlineStr">
+      <c r="X409" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -24289,7 +24319,7 @@
           <t>DONNELLY Sage</t>
         </is>
       </c>
-      <c r="U410" t="inlineStr">
+      <c r="X410" t="inlineStr">
         <is>
           <t>60119</t>
         </is>
@@ -24400,7 +24430,7 @@
           <t>WERATSCHNIG Nadine</t>
         </is>
       </c>
-      <c r="U412" t="inlineStr">
+      <c r="X412" t="inlineStr">
         <is>
           <t>41613</t>
         </is>
@@ -24458,7 +24488,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U413" t="inlineStr">
+      <c r="X413" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -24516,7 +24546,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U414" t="inlineStr">
+      <c r="X414" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -24574,7 +24604,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U415" t="inlineStr">
+      <c r="X415" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -24632,7 +24662,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U416" t="inlineStr">
+      <c r="X416" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -24690,7 +24720,7 @@
           <t>DAWSON Mike</t>
         </is>
       </c>
-      <c r="U417" t="inlineStr">
+      <c r="X417" t="inlineStr">
         <is>
           <t>36656</t>
         </is>
@@ -24748,7 +24778,7 @@
           <t>SWETNAM Huw</t>
         </is>
       </c>
-      <c r="U418" t="inlineStr">
+      <c r="X418" t="inlineStr">
         <is>
           <t>35652</t>
         </is>
@@ -24806,7 +24836,7 @@
           <t>TSVIET Igor</t>
         </is>
       </c>
-      <c r="U419" t="inlineStr">
+      <c r="X419" t="inlineStr">
         <is>
           <t>35527</t>
         </is>
@@ -24864,7 +24894,7 @@
           <t>WEGER Matthias</t>
         </is>
       </c>
-      <c r="U420" t="inlineStr">
+      <c r="X420" t="inlineStr">
         <is>
           <t>68837</t>
         </is>
@@ -24922,7 +24952,7 @@
           <t>MADORE Mathurin</t>
         </is>
       </c>
-      <c r="U421" t="inlineStr">
+      <c r="X421" t="inlineStr">
         <is>
           <t>51994</t>
         </is>
@@ -24980,7 +25010,7 @@
           <t>SILVA Ivan</t>
         </is>
       </c>
-      <c r="U422" t="inlineStr">
+      <c r="X422" t="inlineStr">
         <is>
           <t>35482</t>
         </is>
@@ -25038,7 +25068,7 @@
           <t>MARX Dimitri</t>
         </is>
       </c>
-      <c r="U423" t="inlineStr">
+      <c r="X423" t="inlineStr">
         <is>
           <t>60326</t>
         </is>
@@ -25096,7 +25126,7 @@
           <t>GRIMM Alexander</t>
         </is>
       </c>
-      <c r="U424" t="inlineStr">
+      <c r="X424" t="inlineStr">
         <is>
           <t>35112</t>
         </is>
@@ -25154,7 +25184,7 @@
           <t>BERSINGER Thomas</t>
         </is>
       </c>
-      <c r="U425" t="inlineStr">
+      <c r="X425" t="inlineStr">
         <is>
           <t>35228</t>
         </is>
@@ -25212,7 +25242,7 @@
           <t>SMOLEN Michal</t>
         </is>
       </c>
-      <c r="U426" t="inlineStr">
+      <c r="X426" t="inlineStr">
         <is>
           <t>36397</t>
         </is>
@@ -25270,7 +25300,7 @@
           <t>ADACHI Kazuya</t>
         </is>
       </c>
-      <c r="U427" t="inlineStr">
+      <c r="X427" t="inlineStr">
         <is>
           <t>36646</t>
         </is>
@@ -25328,7 +25358,7 @@
           <t>LEITNER Mario</t>
         </is>
       </c>
-      <c r="U428" t="inlineStr">
+      <c r="X428" t="inlineStr">
         <is>
           <t>35546</t>
         </is>
@@ -25386,7 +25416,7 @@
           <t>SRABOTNIK Martin</t>
         </is>
       </c>
-      <c r="U429" t="inlineStr">
+      <c r="X429" t="inlineStr">
         <is>
           <t>39080</t>
         </is>
@@ -25497,7 +25527,7 @@
           <t>ZIMA Tomas</t>
         </is>
       </c>
-      <c r="U431" t="inlineStr">
+      <c r="X431" t="inlineStr">
         <is>
           <t>60019</t>
         </is>
@@ -25555,7 +25585,7 @@
           <t>JAKSE Zan</t>
         </is>
       </c>
-      <c r="U432" t="inlineStr">
+      <c r="X432" t="inlineStr">
         <is>
           <t>44340</t>
         </is>
@@ -25613,7 +25643,7 @@
           <t>YAZAWA Kazuki</t>
         </is>
       </c>
-      <c r="U433" t="inlineStr">
+      <c r="X433" t="inlineStr">
         <is>
           <t>36482</t>
         </is>
@@ -25671,7 +25701,7 @@
           <t>CRESPO Joan</t>
         </is>
       </c>
-      <c r="U434" t="inlineStr">
+      <c r="X434" t="inlineStr">
         <is>
           <t>35749</t>
         </is>
@@ -25729,7 +25759,7 @@
           <t>POPIELA Dariusz</t>
         </is>
       </c>
-      <c r="U435" t="inlineStr">
+      <c r="X435" t="inlineStr">
         <is>
           <t>35096</t>
         </is>
@@ -25787,7 +25817,7 @@
           <t>CADENA Jordi</t>
         </is>
       </c>
-      <c r="U436" t="inlineStr">
+      <c r="X436" t="inlineStr">
         <is>
           <t>41644</t>
         </is>
@@ -25845,7 +25875,7 @@
           <t>WEGER Jakob</t>
         </is>
       </c>
-      <c r="U437" t="inlineStr">
+      <c r="X437" t="inlineStr">
         <is>
           <t>54909</t>
         </is>
@@ -25903,7 +25933,7 @@
           <t>HRADILEK Vavrinec</t>
         </is>
       </c>
-      <c r="U438" t="inlineStr">
+      <c r="X438" t="inlineStr">
         <is>
           <t>35031</t>
         </is>
@@ -25961,7 +25991,7 @@
           <t>BURGI Quentin</t>
         </is>
       </c>
-      <c r="U439" t="inlineStr">
+      <c r="X439" t="inlineStr">
         <is>
           <t>41590</t>
         </is>
@@ -26019,7 +26049,7 @@
           <t>SCHWEIKERT Fabian</t>
         </is>
       </c>
-      <c r="U440" t="inlineStr">
+      <c r="X440" t="inlineStr">
         <is>
           <t>38412</t>
         </is>
@@ -26130,7 +26160,7 @@
           <t>PASIUT Michal</t>
         </is>
       </c>
-      <c r="U442" t="inlineStr">
+      <c r="X442" t="inlineStr">
         <is>
           <t>35095</t>
         </is>
@@ -26188,7 +26218,7 @@
           <t>HOLMER Erik</t>
         </is>
       </c>
-      <c r="U443" t="inlineStr">
+      <c r="X443" t="inlineStr">
         <is>
           <t>35104</t>
         </is>
@@ -26246,7 +26276,7 @@
           <t>PRINDIS Vit</t>
         </is>
       </c>
-      <c r="U444" t="inlineStr">
+      <c r="X444" t="inlineStr">
         <is>
           <t>35065</t>
         </is>
@@ -26304,7 +26334,7 @@
           <t>OSCHMAUTZ Felix</t>
         </is>
       </c>
-      <c r="U445" t="inlineStr">
+      <c r="X445" t="inlineStr">
         <is>
           <t>51856</t>
         </is>
@@ -26362,7 +26392,7 @@
           <t>GRIGAR Jakub</t>
         </is>
       </c>
-      <c r="U446" t="inlineStr">
+      <c r="X446" t="inlineStr">
         <is>
           <t>37284</t>
         </is>
@@ -26420,7 +26450,7 @@
           <t>DELFOUR Lucien</t>
         </is>
       </c>
-      <c r="U447" t="inlineStr">
+      <c r="X447" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
@@ -26478,7 +26508,7 @@
           <t>SCHUBERT Sebastian</t>
         </is>
       </c>
-      <c r="U448" t="inlineStr">
+      <c r="X448" t="inlineStr">
         <is>
           <t>35114</t>
         </is>
@@ -26536,7 +26566,7 @@
           <t>DE GENNARO Giovanni</t>
         </is>
       </c>
-      <c r="U449" t="inlineStr">
+      <c r="X449" t="inlineStr">
         <is>
           <t>35244</t>
         </is>
@@ -26594,7 +26624,7 @@
           <t>BIAZIZZO Mathieu</t>
         </is>
       </c>
-      <c r="U450" t="inlineStr">
+      <c r="X450" t="inlineStr">
         <is>
           <t>35484</t>
         </is>
@@ -26652,7 +26682,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U451" t="inlineStr">
+      <c r="X451" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -26710,7 +26740,7 @@
           <t>WERRO Lukas</t>
         </is>
       </c>
-      <c r="U452" t="inlineStr">
+      <c r="X452" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
@@ -26768,7 +26798,7 @@
           <t>AIGNER Hannes</t>
         </is>
       </c>
-      <c r="U453" t="inlineStr">
+      <c r="X453" t="inlineStr">
         <is>
           <t>35115</t>
         </is>
@@ -26826,7 +26856,7 @@
           <t>DOUGOUD Martin</t>
         </is>
       </c>
-      <c r="U454" t="inlineStr">
+      <c r="X454" t="inlineStr">
         <is>
           <t>35426</t>
         </is>
@@ -26884,7 +26914,7 @@
           <t>OKREGLAK Maciej</t>
         </is>
       </c>
-      <c r="U455" t="inlineStr">
+      <c r="X455" t="inlineStr">
         <is>
           <t>35088</t>
         </is>
@@ -26942,7 +26972,7 @@
           <t>IVALDI Zeno</t>
         </is>
       </c>
-      <c r="U456" t="inlineStr">
+      <c r="X456" t="inlineStr">
         <is>
           <t>35480</t>
         </is>
@@ -27015,12 +27045,12 @@
           <t>HOCHSCHORNER Peter</t>
         </is>
       </c>
-      <c r="U457" t="inlineStr">
+      <c r="X457" t="inlineStr">
         <is>
           <t>35356</t>
         </is>
       </c>
-      <c r="V457" t="inlineStr">
+      <c r="Y457" t="inlineStr">
         <is>
           <t>35357</t>
         </is>
@@ -27093,12 +27123,12 @@
           <t>HEGER Tomas</t>
         </is>
       </c>
-      <c r="U458" t="inlineStr">
+      <c r="X458" t="inlineStr">
         <is>
           <t>68872</t>
         </is>
       </c>
-      <c r="V458" t="inlineStr">
+      <c r="Y458" t="inlineStr">
         <is>
           <t>42007</t>
         </is>
@@ -27171,12 +27201,12 @@
           <t>BECKER Thomas</t>
         </is>
       </c>
-      <c r="U459" t="inlineStr">
+      <c r="X459" t="inlineStr">
         <is>
           <t>35139</t>
         </is>
       </c>
-      <c r="V459" t="inlineStr">
+      <c r="Y459" t="inlineStr">
         <is>
           <t>35143</t>
         </is>
@@ -27249,12 +27279,12 @@
           <t>PECHE Matthieu</t>
         </is>
       </c>
-      <c r="U460" t="inlineStr">
+      <c r="X460" t="inlineStr">
         <is>
           <t>35350</t>
         </is>
       </c>
-      <c r="V460" t="inlineStr">
+      <c r="Y460" t="inlineStr">
         <is>
           <t>35400</t>
         </is>
@@ -27327,12 +27357,12 @@
           <t>BISO Hugo</t>
         </is>
       </c>
-      <c r="U461" t="inlineStr">
+      <c r="X461" t="inlineStr">
         <is>
           <t>35403</t>
         </is>
       </c>
-      <c r="V461" t="inlineStr">
+      <c r="Y461" t="inlineStr">
         <is>
           <t>35229</t>
         </is>
@@ -27405,12 +27435,12 @@
           <t>TILLARD Pierre-Antoine</t>
         </is>
       </c>
-      <c r="U462" t="inlineStr">
+      <c r="X462" t="inlineStr">
         <is>
           <t>35379</t>
         </is>
       </c>
-      <c r="V462" t="inlineStr">
+      <c r="Y462" t="inlineStr">
         <is>
           <t>35413</t>
         </is>
@@ -27483,12 +27513,12 @@
           <t>SKANTAR Peter</t>
         </is>
       </c>
-      <c r="U463" t="inlineStr">
+      <c r="X463" t="inlineStr">
         <is>
           <t>35360</t>
         </is>
       </c>
-      <c r="V463" t="inlineStr">
+      <c r="Y463" t="inlineStr">
         <is>
           <t>35361</t>
         </is>
@@ -27561,12 +27591,12 @@
           <t>FERRARI Niccolo</t>
         </is>
       </c>
-      <c r="U464" t="inlineStr">
+      <c r="X464" t="inlineStr">
         <is>
           <t>35497</t>
         </is>
       </c>
-      <c r="V464" t="inlineStr">
+      <c r="Y464" t="inlineStr">
         <is>
           <t>35498</t>
         </is>
@@ -27639,12 +27669,12 @@
           <t>SINDLER Marek</t>
         </is>
       </c>
-      <c r="U465" t="inlineStr">
+      <c r="X465" t="inlineStr">
         <is>
           <t>35062</t>
         </is>
       </c>
-      <c r="V465" t="inlineStr">
+      <c r="Y465" t="inlineStr">
         <is>
           <t>35063</t>
         </is>
@@ -27717,12 +27747,12 @@
           <t>BATIK Jan</t>
         </is>
       </c>
-      <c r="U466" t="inlineStr">
+      <c r="X466" t="inlineStr">
         <is>
           <t>35368</t>
         </is>
       </c>
-      <c r="V466" t="inlineStr">
+      <c r="Y466" t="inlineStr">
         <is>
           <t>35367</t>
         </is>
@@ -27790,7 +27820,7 @@
           <t>TIXIER Cecile</t>
         </is>
       </c>
-      <c r="U467" t="inlineStr">
+      <c r="X467" t="inlineStr">
         <is>
           <t>35687</t>
         </is>
@@ -27858,7 +27888,7 @@
           <t>HERZOG Andrea</t>
         </is>
       </c>
-      <c r="U468" t="inlineStr">
+      <c r="X468" t="inlineStr">
         <is>
           <t>55099</t>
         </is>
@@ -27926,7 +27956,7 @@
           <t>KOZOROG Alja</t>
         </is>
       </c>
-      <c r="U469" t="inlineStr">
+      <c r="X469" t="inlineStr">
         <is>
           <t>39986</t>
         </is>
@@ -27994,7 +28024,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U470" t="inlineStr">
+      <c r="X470" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -28125,7 +28155,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U472" t="inlineStr">
+      <c r="X472" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -28193,7 +28223,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U473" t="inlineStr">
+      <c r="X473" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -28324,7 +28354,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U475" t="inlineStr">
+      <c r="X475" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -28392,7 +28422,7 @@
           <t>WERATSCHNIG Nadine</t>
         </is>
       </c>
-      <c r="U476" t="inlineStr">
+      <c r="X476" t="inlineStr">
         <is>
           <t>41613</t>
         </is>
@@ -28460,7 +28490,7 @@
           <t>IVALDI Zeno</t>
         </is>
       </c>
-      <c r="U477" t="inlineStr">
+      <c r="X477" t="inlineStr">
         <is>
           <t>35480</t>
         </is>
@@ -28528,7 +28558,7 @@
           <t>SMOLEN Michal</t>
         </is>
       </c>
-      <c r="U478" t="inlineStr">
+      <c r="X478" t="inlineStr">
         <is>
           <t>36397</t>
         </is>
@@ -28659,7 +28689,7 @@
           <t>GRIGAR Jakub</t>
         </is>
       </c>
-      <c r="U480" t="inlineStr">
+      <c r="X480" t="inlineStr">
         <is>
           <t>37284</t>
         </is>
@@ -28727,7 +28757,7 @@
           <t>TSVIET Igor</t>
         </is>
       </c>
-      <c r="U481" t="inlineStr">
+      <c r="X481" t="inlineStr">
         <is>
           <t>35527</t>
         </is>
@@ -28795,7 +28825,7 @@
           <t>OKREGLAK Maciej</t>
         </is>
       </c>
-      <c r="U482" t="inlineStr">
+      <c r="X482" t="inlineStr">
         <is>
           <t>35088</t>
         </is>
@@ -28863,7 +28893,7 @@
           <t>PRINDIS Vit</t>
         </is>
       </c>
-      <c r="U483" t="inlineStr">
+      <c r="X483" t="inlineStr">
         <is>
           <t>35065</t>
         </is>
@@ -28931,7 +28961,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U484" t="inlineStr">
+      <c r="X484" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -28999,7 +29029,7 @@
           <t>BERSINGER Thomas</t>
         </is>
       </c>
-      <c r="U485" t="inlineStr">
+      <c r="X485" t="inlineStr">
         <is>
           <t>35228</t>
         </is>
@@ -29067,7 +29097,7 @@
           <t>MADORE Mathurin</t>
         </is>
       </c>
-      <c r="U486" t="inlineStr">
+      <c r="X486" t="inlineStr">
         <is>
           <t>51994</t>
         </is>
@@ -29178,7 +29208,7 @@
           <t>SABATTINI Chiara</t>
         </is>
       </c>
-      <c r="U488" t="inlineStr">
+      <c r="X488" t="inlineStr">
         <is>
           <t>35219</t>
         </is>
@@ -29448,7 +29478,7 @@
           <t>TROMPETER Caroline</t>
         </is>
       </c>
-      <c r="U493" t="inlineStr">
+      <c r="X493" t="inlineStr">
         <is>
           <t>39167</t>
         </is>
@@ -29506,7 +29536,7 @@
           <t>FRITSCHE Lisa</t>
         </is>
       </c>
-      <c r="U494" t="inlineStr">
+      <c r="X494" t="inlineStr">
         <is>
           <t>39883</t>
         </is>
@@ -29564,7 +29594,7 @@
           <t>HAMER-EVANS Megan</t>
         </is>
       </c>
-      <c r="U495" t="inlineStr">
+      <c r="X495" t="inlineStr">
         <is>
           <t>55138</t>
         </is>
@@ -29622,7 +29652,7 @@
           <t>HUVELIN Flora</t>
         </is>
       </c>
-      <c r="U496" t="inlineStr">
+      <c r="X496" t="inlineStr">
         <is>
           <t>51787</t>
         </is>
@@ -29680,7 +29710,7 @@
           <t>ZWOLINSKA Klaudia</t>
         </is>
       </c>
-      <c r="U497" t="inlineStr">
+      <c r="X497" t="inlineStr">
         <is>
           <t>42027</t>
         </is>
@@ -29738,7 +29768,7 @@
           <t>MEDON Joanna</t>
         </is>
       </c>
-      <c r="U498" t="inlineStr">
+      <c r="X498" t="inlineStr">
         <is>
           <t>35438</t>
         </is>
@@ -29796,7 +29826,7 @@
           <t>WERATSCHNIG Nina</t>
         </is>
       </c>
-      <c r="U499" t="inlineStr">
+      <c r="X499" t="inlineStr">
         <is>
           <t>41614</t>
         </is>
@@ -29907,7 +29937,7 @@
           <t>WEGMAN Martina</t>
         </is>
       </c>
-      <c r="U501" t="inlineStr">
+      <c r="X501" t="inlineStr">
         <is>
           <t>35345</t>
         </is>
@@ -29965,7 +29995,7 @@
           <t>YAZAWA Aki</t>
         </is>
       </c>
-      <c r="U502" t="inlineStr">
+      <c r="X502" t="inlineStr">
         <is>
           <t>36486</t>
         </is>
@@ -30076,7 +30106,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U504" t="inlineStr">
+      <c r="X504" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -30134,7 +30164,7 @@
           <t>ECKHARDT Kate</t>
         </is>
       </c>
-      <c r="U505" t="inlineStr">
+      <c r="X505" t="inlineStr">
         <is>
           <t>44815</t>
         </is>
@@ -30192,7 +30222,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U506" t="inlineStr">
+      <c r="X506" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -30250,7 +30280,7 @@
           <t>HILGERTOVA Amalie</t>
         </is>
       </c>
-      <c r="U507" t="inlineStr">
+      <c r="X507" t="inlineStr">
         <is>
           <t>36113</t>
         </is>
@@ -30308,7 +30338,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U508" t="inlineStr">
+      <c r="X508" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -30366,7 +30396,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U509" t="inlineStr">
+      <c r="X509" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -30424,7 +30454,7 @@
           <t>LAFONT Marie-Zelia</t>
         </is>
       </c>
-      <c r="U510" t="inlineStr">
+      <c r="X510" t="inlineStr">
         <is>
           <t>35374</t>
         </is>
@@ -30482,7 +30512,7 @@
           <t>KUDEJOVA Katerina</t>
         </is>
       </c>
-      <c r="U511" t="inlineStr">
+      <c r="X511" t="inlineStr">
         <is>
           <t>35034</t>
         </is>
@@ -30540,7 +30570,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U512" t="inlineStr">
+      <c r="X512" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -30598,7 +30628,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U513" t="inlineStr">
+      <c r="X513" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -30656,7 +30686,7 @@
           <t>KRAGELJ Ursa</t>
         </is>
       </c>
-      <c r="U514" t="inlineStr">
+      <c r="X514" t="inlineStr">
         <is>
           <t>36264</t>
         </is>
@@ -30714,7 +30744,7 @@
           <t>DUKATOVA Jana</t>
         </is>
       </c>
-      <c r="U515" t="inlineStr">
+      <c r="X515" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
@@ -30772,7 +30802,7 @@
           <t>SCHORNBERG Jasmin</t>
         </is>
       </c>
-      <c r="U516" t="inlineStr">
+      <c r="X516" t="inlineStr">
         <is>
           <t>35206</t>
         </is>
@@ -30830,7 +30860,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U517" t="inlineStr">
+      <c r="X517" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -30888,7 +30918,7 @@
           <t>LEITNER Lisa</t>
         </is>
       </c>
-      <c r="U518" t="inlineStr">
+      <c r="X518" t="inlineStr">
         <is>
           <t>35305</t>
         </is>
@@ -30946,7 +30976,7 @@
           <t>HORN Stefanie</t>
         </is>
       </c>
-      <c r="U519" t="inlineStr">
+      <c r="X519" t="inlineStr">
         <is>
           <t>38417</t>
         </is>
@@ -31004,7 +31034,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U520" t="inlineStr">
+      <c r="X520" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -31062,7 +31092,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U521" t="inlineStr">
+      <c r="X521" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -31120,7 +31150,7 @@
           <t>KUHNLE Corinna</t>
         </is>
       </c>
-      <c r="U522" t="inlineStr">
+      <c r="X522" t="inlineStr">
         <is>
           <t>35282</t>
         </is>
@@ -31178,7 +31208,7 @@
           <t>BORROWS Ian</t>
         </is>
       </c>
-      <c r="U523" t="inlineStr">
+      <c r="X523" t="inlineStr">
         <is>
           <t>36534</t>
         </is>
@@ -31236,7 +31266,7 @@
           <t>JANE Michal</t>
         </is>
       </c>
-      <c r="U524" t="inlineStr">
+      <c r="X524" t="inlineStr">
         <is>
           <t>35059</t>
         </is>
@@ -31294,7 +31324,7 @@
           <t>MAJERCZAK Grzegorz</t>
         </is>
       </c>
-      <c r="U525" t="inlineStr">
+      <c r="X525" t="inlineStr">
         <is>
           <t>35086</t>
         </is>
@@ -31352,7 +31382,7 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U526" t="inlineStr">
+      <c r="X526" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -31410,7 +31440,7 @@
           <t>CORREA Charles</t>
         </is>
       </c>
-      <c r="U527" t="inlineStr">
+      <c r="X527" t="inlineStr">
         <is>
           <t>38018</t>
         </is>
@@ -31468,7 +31498,7 @@
           <t>LOKKEN Zachary</t>
         </is>
       </c>
-      <c r="U528" t="inlineStr">
+      <c r="X528" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
@@ -31526,7 +31556,7 @@
           <t>ROISIN Lucas</t>
         </is>
       </c>
-      <c r="U529" t="inlineStr">
+      <c r="X529" t="inlineStr">
         <is>
           <t>55580</t>
         </is>
@@ -31584,7 +31614,7 @@
           <t>BADURA Jergus</t>
         </is>
       </c>
-      <c r="U530" t="inlineStr">
+      <c r="X530" t="inlineStr">
         <is>
           <t>68767</t>
         </is>
@@ -31642,7 +31672,7 @@
           <t>LENARCIC Jure</t>
         </is>
       </c>
-      <c r="U531" t="inlineStr">
+      <c r="X531" t="inlineStr">
         <is>
           <t>36259</t>
         </is>
@@ -31700,7 +31730,7 @@
           <t>ROHAN Lukas</t>
         </is>
       </c>
-      <c r="U532" t="inlineStr">
+      <c r="X532" t="inlineStr">
         <is>
           <t>36114</t>
         </is>
@@ -31758,7 +31788,7 @@
           <t>CHALOUPKA Vaclav</t>
         </is>
       </c>
-      <c r="U533" t="inlineStr">
+      <c r="X533" t="inlineStr">
         <is>
           <t>51648</t>
         </is>
@@ -31816,7 +31846,7 @@
           <t>SMEDLEY Cameron</t>
         </is>
       </c>
-      <c r="U534" t="inlineStr">
+      <c r="X534" t="inlineStr">
         <is>
           <t>35543</t>
         </is>
@@ -31874,7 +31904,7 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U535" t="inlineStr">
+      <c r="X535" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -31932,7 +31962,7 @@
           <t>WATKINS Daniel</t>
         </is>
       </c>
-      <c r="U536" t="inlineStr">
+      <c r="X536" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -31990,7 +32020,7 @@
           <t>IVALDI Raffaello</t>
         </is>
       </c>
-      <c r="U537" t="inlineStr">
+      <c r="X537" t="inlineStr">
         <is>
           <t>35227</t>
         </is>
@@ -32048,7 +32078,7 @@
           <t>BOZIC Luka</t>
         </is>
       </c>
-      <c r="U538" t="inlineStr">
+      <c r="X538" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
@@ -32106,7 +32136,7 @@
           <t>HEDWIG Grzegorz</t>
         </is>
       </c>
-      <c r="U539" t="inlineStr">
+      <c r="X539" t="inlineStr">
         <is>
           <t>35465</t>
         </is>
@@ -32217,7 +32247,7 @@
           <t>ANTON Franz</t>
         </is>
       </c>
-      <c r="U541" t="inlineStr">
+      <c r="X541" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
@@ -32275,7 +32305,7 @@
           <t>BERCIC Anze</t>
         </is>
       </c>
-      <c r="U542" t="inlineStr">
+      <c r="X542" t="inlineStr">
         <is>
           <t>36253</t>
         </is>
@@ -32333,7 +32363,7 @@
           <t>KOECHLIN Thomas</t>
         </is>
       </c>
-      <c r="U543" t="inlineStr">
+      <c r="X543" t="inlineStr">
         <is>
           <t>35419</t>
         </is>
@@ -32444,7 +32474,7 @@
           <t>THOMAS Martin</t>
         </is>
       </c>
-      <c r="U545" t="inlineStr">
+      <c r="X545" t="inlineStr">
         <is>
           <t>35412</t>
         </is>
@@ -32502,7 +32532,7 @@
           <t>SLAFKOVSKY Alexander</t>
         </is>
       </c>
-      <c r="U546" t="inlineStr">
+      <c r="X546" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
@@ -32560,7 +32590,7 @@
           <t>CIPRESSI Stefano</t>
         </is>
       </c>
-      <c r="U547" t="inlineStr">
+      <c r="X547" t="inlineStr">
         <is>
           <t>35495</t>
         </is>
@@ -32618,7 +32648,7 @@
           <t>MARTIKAN Michal</t>
         </is>
       </c>
-      <c r="U548" t="inlineStr">
+      <c r="X548" t="inlineStr">
         <is>
           <t>35365</t>
         </is>
@@ -32676,7 +32706,7 @@
           <t>TASIADIS Sideris</t>
         </is>
       </c>
-      <c r="U549" t="inlineStr">
+      <c r="X549" t="inlineStr">
         <is>
           <t>35135</t>
         </is>
@@ -32734,7 +32764,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U550" t="inlineStr">
+      <c r="X550" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -32792,7 +32822,7 @@
           <t>COLAZINGARI Roberto</t>
         </is>
       </c>
-      <c r="U551" t="inlineStr">
+      <c r="X551" t="inlineStr">
         <is>
           <t>35223</t>
         </is>
@@ -32850,7 +32880,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U552" t="inlineStr">
+      <c r="X552" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -32918,7 +32948,7 @@
           <t>KRAGELJ Ursa</t>
         </is>
       </c>
-      <c r="U553" t="inlineStr">
+      <c r="X553" t="inlineStr">
         <is>
           <t>36264</t>
         </is>
@@ -32986,7 +33016,7 @@
           <t>ECKHARDT Kate</t>
         </is>
       </c>
-      <c r="U554" t="inlineStr">
+      <c r="X554" t="inlineStr">
         <is>
           <t>44815</t>
         </is>
@@ -33054,7 +33084,7 @@
           <t>HORN Stefanie</t>
         </is>
       </c>
-      <c r="U555" t="inlineStr">
+      <c r="X555" t="inlineStr">
         <is>
           <t>38417</t>
         </is>
@@ -33122,7 +33152,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U556" t="inlineStr">
+      <c r="X556" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -33190,7 +33220,7 @@
           <t>LEITNER Lisa</t>
         </is>
       </c>
-      <c r="U557" t="inlineStr">
+      <c r="X557" t="inlineStr">
         <is>
           <t>35305</t>
         </is>
@@ -33258,7 +33288,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U558" t="inlineStr">
+      <c r="X558" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -33326,7 +33356,7 @@
           <t>LAFONT Marie-Zelia</t>
         </is>
       </c>
-      <c r="U559" t="inlineStr">
+      <c r="X559" t="inlineStr">
         <is>
           <t>35374</t>
         </is>
@@ -33394,7 +33424,7 @@
           <t>DUKATOVA Jana</t>
         </is>
       </c>
-      <c r="U560" t="inlineStr">
+      <c r="X560" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
@@ -33462,7 +33492,7 @@
           <t>WEGMAN Martina</t>
         </is>
       </c>
-      <c r="U561" t="inlineStr">
+      <c r="X561" t="inlineStr">
         <is>
           <t>35345</t>
         </is>
@@ -33530,7 +33560,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U562" t="inlineStr">
+      <c r="X562" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -33598,7 +33628,7 @@
           <t>MAJERCZAK Grzegorz</t>
         </is>
       </c>
-      <c r="U563" t="inlineStr">
+      <c r="X563" t="inlineStr">
         <is>
           <t>35086</t>
         </is>
@@ -33666,7 +33696,7 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U564" t="inlineStr">
+      <c r="X564" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -33734,7 +33764,7 @@
           <t>IVALDI Raffaello</t>
         </is>
       </c>
-      <c r="U565" t="inlineStr">
+      <c r="X565" t="inlineStr">
         <is>
           <t>35227</t>
         </is>
@@ -33802,7 +33832,7 @@
           <t>BADURA Jergus</t>
         </is>
       </c>
-      <c r="U566" t="inlineStr">
+      <c r="X566" t="inlineStr">
         <is>
           <t>68767</t>
         </is>
@@ -33870,7 +33900,7 @@
           <t>MARTIKAN Michal</t>
         </is>
       </c>
-      <c r="U567" t="inlineStr">
+      <c r="X567" t="inlineStr">
         <is>
           <t>35365</t>
         </is>
@@ -33938,7 +33968,7 @@
           <t>ROHAN Lukas</t>
         </is>
       </c>
-      <c r="U568" t="inlineStr">
+      <c r="X568" t="inlineStr">
         <is>
           <t>36114</t>
         </is>
@@ -34006,7 +34036,7 @@
           <t>TASIADIS Sideris</t>
         </is>
       </c>
-      <c r="U569" t="inlineStr">
+      <c r="X569" t="inlineStr">
         <is>
           <t>35135</t>
         </is>
@@ -34074,7 +34104,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U570" t="inlineStr">
+      <c r="X570" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -34142,7 +34172,7 @@
           <t>SLAFKOVSKY Alexander</t>
         </is>
       </c>
-      <c r="U571" t="inlineStr">
+      <c r="X571" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
@@ -34210,7 +34240,7 @@
           <t>BOZIC Luka</t>
         </is>
       </c>
-      <c r="U572" t="inlineStr">
+      <c r="X572" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
